--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E432"/>
+  <dimension ref="A1:E429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>The genes sequenced were integrase (IN) and protease/reverse transcriptase (PR/RT) regions.</t>
+          <t>The HIV genes sequenced were integrase (IN) and protease/reverse transcriptase (PR/RT) regions.</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Plasma and dried blood spots (DBS) were sequenced.</t>
+          <t>Both plasma and dried blood spots (DBS) were sequenced.</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure.</t>
+          <t>Yes, sequences were obtained from individuals with virological failure on a treatment regimen.</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Samples were obtained from 488 individuals for HIV sequencing.</t>
+          <t>234 individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Yes, the paper reports sequences from individuals who had previously received ARV drugs.</t>
+          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Individuals received NRTIs and Integrase Strand Transfer Inhibitors (INSTIs).</t>
+          <t>Individuals received Integrase Strand Transfer Inhibitors (INSTIs), Nucleos(t)ide Reverse Transcriptase Inhibitors (NRTIs), and Protease Inhibitors (PIs) before sample sequencing.</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>TDF, 3TC, DTG, RAL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Individuals received tenofovir, lamivudine, and dolutegravir, and raltegravir.</t>
+          <t>Yes, the sequences were made publicly available.</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4456,22 +4456,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, RAL</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Yes, sequences were made publicly available.</t>
+          <t>The samples were obtained from England.</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4486,13 +4486,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>The paper mentions the M184I/V and K103Q mutations in HIV genes, indicating sequencing of the reverse transcriptase gene for K103Q and protease for M184I.</t>
+          <t>The samples were obtained between October 13, 2017, and July 12, 2020.</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4507,17 +4511,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>2017-2020</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from England, as the trial was conducted across Sexual Health Services in England.</t>
+          <t>The paper does not specify the sequencing method used.</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4532,17 +4536,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>RT,IN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from participants diagnosed between 2017 and 2020.</t>
+          <t>The paper does not specify the type of samples sequenced.</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4557,17 +4561,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2017-2020</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>The paper does not specify the exact sequencing method used for genotypic resistance profiling.</t>
+          <t>Yes, the paper describes a clinical trial.</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4582,17 +4586,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>RT,IN</t>
+          <t>Yes (PrEP)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of clinical specimens sequenced, whether blood or other fluids.</t>
+          <t>Samples were obtained from 54 participants who were diagnosed with HIV during the trial.</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4607,17 +4611,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Yes, the paper indicates that there were participants who experienced virological failure.</t>
+          <t>The paper reports on PrEP usage but does not detail other drug classes received before sampling.</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4632,17 +4636,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Yes, the patients were part of the PrEP Impact trial.</t>
+          <t>The individuals in the study received oral PrEP consisting of tenofovir disoproxil fumarate and emtricitabine.</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4652,22 +4656,18 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Yes (PrEP)</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Samples were obtained from 54 participants who were diagnosed with HIV during the trial.</t>
+          <t>The paper reports sequencing of the protease and reverse transcriptase genes. It also discusses mutations in the integrase gene, indicating that the integrase gene was analyzed for resistance mutations.</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4677,22 +4677,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Yes, the paper mentions participants who had been on PrEP, which involves antiretroviral drugs.</t>
+          <t>The sequenced samples were obtained from Switzerland, as indicated by the mention of the Swiss HIV Cohort Study and the biobank from which the samples were sourced.</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4702,22 +4702,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Participants received NRTIs and presumably INSTIs or PIs as part of their PrEP or post-seroconversion regimens.</t>
+          <t>The sequenced samples were obtained from various years, with specific dates mentioned in the context of genotypic resistance tests. Key dates include 2006, 2022, 2023, and 2024.</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -4727,22 +4727,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>2006-2024</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Specific drugs received included TDF, FTC, DTG, DRV, 3TC, ABC, and RAL, reflecting the treatments received prior to HIV sequencing.</t>
+          <t>The paper mentions the use of next-generation sequencing (NGS) for genotypic resistance testing. This indicates that NGS was the method employed for sequencing the HIV genomes.</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4757,13 +4757,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>The HIV protease and reverse transcriptase genes were sequenced.</t>
+          <t>Yes, the paper discusses sequences obtained from an individual with virological failure on a treatment regimen. It describes the emergence of resistance mutations following virological failure on a quadruple regimen including bictegravir and doravirine.</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4778,17 +4782,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Switzerland.</t>
+          <t>Yes, the paper mentions that the patient was enrolled in the Swiss HIV Cohort Study and participated in the TMC-125 trial, indicating that some aspects of the patient's treatment were part of a clinical trial.</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4803,17 +4807,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from 2022-2024.</t>
+          <t>The paper focuses on a single case study of one individual, indicating that samples were obtained from this one patient for HIV sequencing.</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4828,17 +4832,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2006-2024</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Next generation sequencing was used for genotypic resistance tests.</t>
+          <t>Yes, the paper reports HIV sequences from an individual who had previously received multiple antiretroviral (ARV) drugs. The patient described in the study is treatment-experienced and had received various ARV drugs over the years.</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4853,17 +4857,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>RT, PR, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Plasma RNA and proviral DNA from PBMCs were sequenced.</t>
+          <t>The individual in the study received NRTIs, NNRTIs, PIs, and INSTIs before sample sequencing. The paper discusses the evolution of resistance across these drug classes over time.</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -4878,17 +4882,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Yes, the paper discusses sequences obtained from an individual with virological failure.</t>
+          <t>The individual in the study received a variety of ARV drugs over the years, including zidovudine, ritonavir, didanosine, abacavir, tenofovir disoproxil, lopinavir/ritonavir, etravirine, raltegravir, tenofovir alafenamide, emtricitabine, elvitegravir, darunavir, bictegravir, and doravirine.</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4898,22 +4902,18 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Yes, the patient was enrolled in the Swiss HIV Cohort Study and participated in the TMC-125 trial.</t>
+          <t>The study sequenced the protease and reverse-transcriptase regions of the HIV-1 pol gene.</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4923,22 +4923,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>One individual had samples obtained for HIV sequencing.</t>
+          <t>The sequenced samples were obtained from Argentina.</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -4948,22 +4948,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Yes, the paper discusses sequences from an individual who had previously received ARV drugs.</t>
+          <t>The samples were collected between 2017 and 2021.</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -4973,22 +4973,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2017-2021</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NRTIs, PIs, NNRTIs, and INSTIs were received before sample sequencing.</t>
+          <t>The sequencing was performed using an Applied Biosystems/Hitachi 3500 Genetic Analyzer.</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -4998,22 +4998,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>RT,PR</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), ritonavir (RTV), didanosine (ddI), abacavir (ABC), tenofovir disoproxil (TDF), lopinavir (LPV), etravirine (ETR), atazanavir (ATV), raltegravir (RAL), emtricitabine (FTC), dolutegravir (DTG), darunavir (DRV), and bictegravir (BIC).</t>
+          <t>Plasma samples were sequenced.</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5028,13 +5028,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the HIV-1 pol gene, specifically the protease and reverse-transcriptase regions.</t>
+          <t>Samples from 1667 individuals were analyzed.</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5044,22 +5048,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Argentina.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates are not reported in the provided text.</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5069,22 +5073,18 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained between 2017 and 2021.</t>
+          <t>The genes sequenced include protease and reverse transcriptase as indicated by the resistance mutations analyzed in those genes.</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5094,22 +5094,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2017-2021</t>
+          <t>187</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>The paper used a PCR-based method for sequencing the HIV-1 pol gene fragments.</t>
+          <t>The sequenced samples were obtained from Kenya, specifically through the Academic Model Providing Access to Healthcare in western Kenya.</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5119,22 +5119,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>RT,PR</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced in the study.</t>
+          <t>The sequenced samples were obtained from 2011 to 2021.</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5144,22 +5144,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2011-2021</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Samples from 1667 individuals were included in the mutation analysis.</t>
+          <t>Sanger sequencing was used for sequencing the HIV samples.</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5174,13 +5174,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>The paper mentions that the protease and reverse transcriptase genes were sequenced for resistance mutations.</t>
+          <t>Plasma HIV-1 RNA samples were sequenced.</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -5195,17 +5199,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Kenya, specifically from the Academic Model Providing Access to Healthcare in western Kenya.</t>
+          <t>Yes, the sequences were obtained from individuals with virological failure on a treatment regimen.</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5220,17 +5224,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from 2011 to 2021.</t>
+          <t>A total of 187 individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5245,17 +5249,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2011-2021</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>The paper mentions that Sanger sequencing was used for analyzing the HIV-1 RNA samples.</t>
+          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5270,17 +5274,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>The paper mentions that plasma HIV-1 RNA samples were sequenced.</t>
+          <t>Individuals received NRTI, NNRTI, and PI drug classes before sample sequencing; dual-class and triple-class resistance were also reported</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5295,17 +5299,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Yes, the paper focuses on individuals with second-line viral failure (VF) who underwent genotyping.</t>
+          <t>The drugs received included atazanavir/ritonavir, lopinavir/ritonavir, lamivudine, tenofovir, nevirapine, and zidovudine, abacavir</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5315,22 +5319,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>The paper included data from 187 individuals who had genotypes performed for HIV sequencing.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates are not provided in the abstract or materials and methods of the paper.</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5340,22 +5344,18 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Yes, the paper included individuals who had extensive antiretroviral therapy (ART) experience, including those who failed second-line regimens.</t>
+          <t>The genes sequenced include the envelope (env), gag, and pol proteins for genotyping and the protease, reverse transcriptase, and integrase genes for drug resistance analysis.</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5365,22 +5365,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The paper participants received NRTI, NNRTI, and PI drug classes prior to sequencing.</t>
+          <t>The sequenced samples were obtained from South Korea, with a significant portion from non-Korean individuals primarily from Asia and the Americas.</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for the sequenced HIV isolates are not provided in the text.</t>
+          <t>The sequenced samples were obtained from the years 2021 to 2024.</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5420,13 +5420,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2021-2024</t>
+        </is>
+      </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the envelope (env), gag, pol, protease, reverse transcriptase, and integrase genes.</t>
+          <t>Sanger sequencing was performed using in-house sequencing primers.</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5441,17 +5445,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from South Korea, with a distinction between Korean and non-Korean patients.</t>
+          <t>Viral RNA was extracted from plasma or serum samples.</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5466,17 +5470,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from the years 2021 to 2024.</t>
+          <t>Samples were obtained from 487 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5491,17 +5495,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The method used for sequencing was Sanger sequencing.</t>
+          <t>The study included ART-naïve individuals, so no drug classes were received before sample sequencing.</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5516,17 +5520,13 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>PR, RT, IN</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The type of samples sequenced were plasma or serum from patients.</t>
+          <t>The study included ART-naïve individuals, so no specific drugs were received before sample sequencing.</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5536,22 +5536,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Samples were obtained from 487 individuals for HIV sequencing.</t>
+          <t>The GenBank accession numbers for the sequenced HIV isolates are PV526713-PV526742.</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5561,22 +5561,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PV526713-PV526742</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>The study included individuals who were ART-naïve at the time of sample sequencing, so they had not received any drug classes before sequencing.</t>
+          <t>The HIV pol region, specifically the protease and reverse transcriptase (PR/RT) genes, were sequenced.</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5586,18 +5586,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>The study included individuals who were ART-naïve at the time of sample sequencing, so they had not received any drugs before sequencing.</t>
+          <t>The sequenced samples were obtained from Brazil.</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5612,17 +5616,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are PV526713-PV526742.</t>
+          <t>The sequenced samples were obtained from 2007 to 2022.</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5637,17 +5641,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>PV526713-PV526742</t>
+          <t>2007-2022</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>The genes sequenced are the protease/reverse transcriptase (PR/RT) region of HIV.</t>
+          <t>The ViroSeq Genotyping System was used for sequencing.</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5662,17 +5666,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Brazil.</t>
+          <t>Clinical samples from mother-child pairs with confirmed vertical transmission of HIV-1 were sequenced.</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5687,17 +5691,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from 2007 to 2022.</t>
+          <t>Yes, some mothers in the study had virological failure and required genotyping.</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5712,17 +5716,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2007-2022</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>The sequencing method used was the ViroSeq Genotyping System.</t>
+          <t>Samples were obtained from 15 mother-child pairs, totaling 30 individuals.</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5737,17 +5741,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>The sequenced samples were clinical specimens from mother-child pairs with confirmed vertical transmission of HIV-1.</t>
+          <t>Yes, the paper includes mothers who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5762,17 +5766,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure on a treatment regimen.</t>
+          <t>Individuals in the study received drugs from the NRTI and NNRTI classes.</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -5787,17 +5791,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Samples were obtained from 15 mother-child pairs, totaling 30 individuals.</t>
+          <t>Individuals received zidovudine (ZDV), lamivudine (3TC), nevirapine (NVP), lopinavir/ritonavir, and efavirenz (EFV).</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5812,17 +5816,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>Yes, the GenBank accession numbers provided indicate that the sequences were made publicly available.</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5832,22 +5836,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40713598</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Individuals in the study received nucleoside reverse transcriptase inhibitors (NRTIs) and non-nucleoside reverse transcriptase inhibitors (NNRTIs) before sample sequencing.</t>
+          <t>The GenBank accession numbers are not provided in the content of the paper. The study did not mention any accession numbers for the sequenced HIV isolates.</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5857,22 +5861,18 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40713598</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Individuals in the study received zidovudine (ZDV), lamivudine (3TC), nevirapine (NVP), lopinavir/ritonavir, and efavirenz (EFV) before sample sequencing.</t>
+          <t>The HIV-1 pol gene was sequenced, encompassing the protease (PR) and reverse transcriptase (RT) regions.</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5882,22 +5882,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40713598</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Yes, the sequences were made publicly available through GenBank.</t>
+          <t>The sequenced samples were obtained from Ghana, specifically from the Pediatric HIV/AIDS Care Program at Korle-Bu Teaching Hospital in Ghana.</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5912,17 +5912,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>HIV drug resistance (HIVDR) was retrospectively characterized among 20 children and adolescents with HIV with virologic failure on non-nucleoside reverse transcriptase inhibitor (NNRTI)-based therapy, and virologic response in those switched to dolutegravir (DTG)-based therapy described.</t>
+          <t>The specific years from which the sequenced samples were obtained are not mentioned in the paper.</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5937,13 +5937,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>The HIV-1 pol gene was sequenced.</t>
+          <t>Next-generation sequencing (NGS) was conducted on the Illumina MiSeq platform.</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -5958,17 +5962,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>The samples were obtained from Ghana.</t>
+          <t>Frozen plasma samples were used for sequencing.</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -5983,17 +5987,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>The study does not specify the exact years from which the samples were obtained.</t>
+          <t>Yes, the paper reports sequences obtained from individuals with virological failure on a treatment regimen. It specifically focuses on children and adolescents with virologic failure on NNRTI-based therapy.</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6008,17 +6012,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Next-generation sequencing (NGS) using the Illumina MiSeq platform was used.</t>
+          <t>Samples were attempted from 96 individuals with HIV-1 RNA &gt;1,000 copies/ml, but 20 samples were successfully amplified and sequenced.</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6033,17 +6037,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs. It discusses resistance in children and adolescents on NNRTI-based antiretroviral therapy.</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6058,17 +6062,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Yes, the study focuses on individuals with virological failure.</t>
+          <t>Individuals in the study received non-nucleoside reverse transcriptase inhibitors (NNRTIs) and nucleoside reverse transcriptase inhibitors (NRTIs) before sample sequencing.</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6083,17 +6087,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Samples were obtained from 20 individuals.</t>
+          <t>Specific drugs received by individuals included nevirapine, efavirenz, lamivudine, tenofovir, abacavir, and zidovudine before sample sequencing.</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6103,22 +6107,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Yes, the paper includes individuals who had previously received ARV drugs.</t>
+          <t>No, the paper does not report HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6128,22 +6132,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Individuals received non-nucleoside reverse transcriptase inhibitors (NNRTIs) and nucleoside reverse transcriptase inhibitors (NRTIs).</t>
+          <t>The paper does not mention sequenced samples from any country.</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6153,22 +6157,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>The specific drugs received include Abacavir (ABC), Lamivudine (3TC), Nevirapine (NVP), Zidovudine (ZDV), and Efavirenz (EFV).</t>
+          <t>The paper does not provide information on the years from which sequenced samples were obtained.</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6183,17 +6187,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2021-2023</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Uganda.</t>
+          <t>The study used Sanger sequencing or Next Generation Sequencing.</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -6208,17 +6212,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained between 2021 and 2023.</t>
+          <t>The study used plasma or dried blood spot (DBS) samples for sequencing.</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -6233,17 +6237,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>Sanger, NGS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>The paper mentions the use of Sanger sequencing or Next Generation Sequencing (NGS) for identifying mutations.</t>
+          <t>Yes, the paper reports sequences from individuals with virological failure.</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -6258,17 +6262,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Plasma or dried blood spot (DBS) samples were sequenced.</t>
+          <t>295 individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6283,17 +6287,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Yes, the sequences were obtained from individuals with virological failure.</t>
+          <t>Yes, the paper includes participants who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6308,7 +6312,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6318,7 +6322,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>A total of 295 individuals had samples obtained for HIV sequencing.</t>
+          <t>Individuals received NRTIs, NNRTIs, PIs, and INSTIs before sample sequencing.</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -6333,17 +6337,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>Drugs received included Abacavir, Lamivudine, Zidovudine, Tenofovir, Dolutegravir, Atazanavir, Lopinavir, and Darunavir.</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -6353,22 +6357,18 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Individuals in the study received NRTI, NNRTI, PI, and INSTI drug classes before sample sequencing.</t>
+          <t>The HIV genes reported to have been sequenced include protease (PR), reverse transcriptase (RT), and integrase (IN).</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -6378,22 +6378,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>The study involved participants on various ART regimens including TDF/3TC/DTG, AZT/3TC/DTG, ABC/3TC/DTG, ABC/3TC/LPVr, TDF/3TC/ATVr, AZT/3TC/ATVr, and others before sample sequencing.</t>
+          <t>The paper does not specify the countries from which the sequenced samples were obtained.</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6408,13 +6408,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>The HIV genes reported to have been sequenced include protease (PR), reverse transcriptase (RT), and integrase (IN).</t>
+          <t>The sequencing method used was next-generation sequencing (NGS).</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6429,17 +6433,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>The paper does not specify the countries from which the sequenced samples were obtained.</t>
+          <t>Whole blood samples were sequenced for proviral DNA.</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6454,17 +6458,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>The study used population sequencing level.</t>
+          <t>Yes, the patients were part of Phase 2/3/3b clinical trials.</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6479,17 +6483,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>The paper mentions that whole blood samples were used for sequencing.</t>
+          <t>Samples were obtained from 2028 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6504,17 +6508,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Yes, the patients were part of Phase 2/3/3b clinical trials.</t>
+          <t>Participants received NRTIs, INSTIs, NNRTIs, and protease inhibitors (PIs) before sample sequencing.</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -6524,22 +6528,18 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40839365</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Samples were obtained from 2028 individuals for HIV sequencing.</t>
+          <t>The genes sequenced were protease, reverse transcriptase, and integrase.</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6549,22 +6549,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40839365</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>212</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Participants received NRTIs, INSTIs, NNRTIs, and PI before sample sequencing.</t>
+          <t>The sequenced samples were obtained from Malawi.</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6579,13 +6579,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Protease, reverse transcriptase, and integrase genes were sequenced.</t>
+          <t>The samples were obtained between July 2022 and February 2023.</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6600,17 +6604,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>2022-2023</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Malawi.</t>
+          <t>The study used Sanger sequencing for genotypic analysis.</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -6625,17 +6629,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>The samples were obtained between July 2022 and February 2023.</t>
+          <t>Plasma samples were sequenced.</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -6650,17 +6654,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Sanger sequencing method was used.</t>
+          <t>Yes, sequences were obtained from individuals with virological failure on a treatment regimen.</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -6675,17 +6679,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>Samples were obtained from 213 individuals with confirmed virologic failure.</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -6700,17 +6704,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with confirmed virological failure.</t>
+          <t>Yes, the paper reports sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -6725,7 +6729,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6735,7 +6739,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Samples were obtained from 213 individuals with confirmed virologic failure.</t>
+          <t>Individuals in the study received drugs from the NRTI, NNRTI, PI, and INSTI classes before sample sequencing.</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -6750,17 +6754,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Yes, the paper includes individuals who had previously received ARV drugs.</t>
+          <t>The specific drugs received by individuals prior to sequencing are not listed in the provided text.</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -6770,22 +6774,18 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Individuals received NRTIs, NNRTIs, PIs, and INSTIs before sample sequencing.</t>
+          <t>Protease (PR), reverse transcriptase (RT), and integrase (IN) genes were sequenced.</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6795,22 +6795,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>7 (Uncertain)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Individuals received drugs such as abacavir, emtricitabine, lamivudine, stavudine, tenofovir disoproxil fumarate, efavirenz, nevirapine, cabotegravir, and dolutegravir.</t>
+          <t>Countries were not specified in the provided content.</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -6825,13 +6825,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the protease (PR), reverse transcriptase (RT), and integrase (IN) genes.</t>
+          <t>The years of sample collection are not specified.</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -6846,17 +6850,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>The paper does not specify the countries from which the sequenced samples were obtained.</t>
+          <t>Clinical samples were sequenced.</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -6871,17 +6875,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>The paper does not detail the specific method used for sequencing.</t>
+          <t>Yes, sequences were obtained from individuals with virological failure.</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -6896,17 +6900,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples that were sequenced.</t>
+          <t>Yes, the study was a clinical trial.</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -6921,17 +6925,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Yes, the paper mentions sequences were obtained from individuals with virologic failure.</t>
+          <t>The paper mentions that data were available for at least 19 individuals.</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -6946,17 +6950,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Yes, the study was a phase 3 randomized trial.</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -6971,17 +6975,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>The paper mentions resistance testing data for 22 participants.</t>
+          <t>Bictegravir, Emtricitabine, Tenofovir Alafenamide, Dolutegravir, Emtricitabine, Tenofovir Disoproxil Fumarate</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -6991,22 +6995,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>The individuals in the study received integrase inhibitors, NRTIs, and non-NRTIs.</t>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -7016,22 +7020,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>The drugs received include bictegravir, emtricitabine, tenofovir alafenamide, dolutegravir, and tenofovir disoproxil fumarate.</t>
+          <t>The paper reports the sequencing of drug resistance mutations Including RT, PR, and IN genes.</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -7046,17 +7050,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0 (Review paper)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Yes the paper reports HIV sequences from patient samples.</t>
+          <t>The sequenced samples were obtained from Tanzania.</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -7071,17 +7075,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the RT and integrase gene.</t>
+          <t>The sequenced samples were obtained from studies published until the end of December 2024.</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -7096,17 +7100,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0 (Review paper)</t>
+          <t>2004-2021</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Tanzania.</t>
+          <t>The paper does not specify the exact method used for sequencing.</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -7121,17 +7125,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from studies published up to 2024, covering various years including 2005-2021.</t>
+          <t>The paper does not specify the type of clinical samples that were sequenced.</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -7146,17 +7150,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>The paper does not specify the exact sequencing method used.</t>
+          <t>Yes, the paper reports sequences obtained from individuals with virological failure on a treatment regimen.</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -7171,17 +7175,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of clinical samples sequenced.</t>
+          <t>The paper mentions that the meta-analysis included studies with a total of 9685 participants on ART.</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -7196,17 +7200,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Yes, the paper reports sequences obtained from individuals with virological failure on a treatment regimen.</t>
+          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -7221,7 +7225,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7231,7 +7235,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>A total of 9685 individuals had samples obtained for HIV sequencing.</t>
+          <t>The paper reports the receipt of NRTIs and NNRTIs by individuals in the study before sample sequencing.</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -7246,17 +7250,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>The paper mentions the use of various NRTIs including 3TC, FTC, AZT, and TDF.</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -7266,12 +7270,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7281,7 +7285,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>The individuals in the study received NRTIs, NNRTIs, PIs, and INSTIs before sample sequencing.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates are PX133190-PX134237.</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -7291,22 +7295,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>PX133190–PX134237</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>The drugs received by individuals in the study include TDF, 3TC, DTG, FTC, AZT, and LPV/r.</t>
+          <t>The paper reports the sequencing of the pol gene, which includes the full-length protease (PR) and the first 299 codons of the RT gene.</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -7321,17 +7325,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>GenBank accession numbers for sequenced HIV isolates are PX133190-PX134237.</t>
+          <t>The sequenced samples were obtained from China, specifically Nanning City, Guangxi Province.</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -7346,17 +7350,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>PX133190–PX134237</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>The pol gene was sequenced.</t>
+          <t>The sequenced samples were obtained from 2019 to 2022.</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -7371,17 +7375,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>2019-2022</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Samples were obtained from China.</t>
+          <t>The method used for sequencing was Sanger sequencing, conducted by Sangon Biotech using the Applied Biosystems 3730XL Genetic Analyzer.</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -7396,17 +7400,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Samples were obtained from 2019 to 2022.</t>
+          <t>Plasma samples were sequenced in this study. HIV-1 RNA was extracted from plasma samples for sequencing.</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -7421,17 +7425,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2019-2022</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Sanger sequencing was used.</t>
+          <t>Samples were obtained from 1,260 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -7446,17 +7450,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>The study did not have individuals who received antiretroviral drugs before sample sequencing, as it focused on newly diagnosed, ART-naive individuals.</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -7471,17 +7475,13 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Samples were obtained from 1,260 individuals.</t>
+          <t>The study did not have individuals who received antiretroviral drugs before sample sequencing, as it focused on newly diagnosed, ART-naive individuals.</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -7502,7 +7502,7 @@
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Yes, sequences were made publicly available.</t>
+          <t>Yes, the sequences were made publicly available and are listed under specific GenBank accession numbers.</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -7517,17 +7517,13 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>There were no GenBank accession numbers.</t>
+          <t>The study reported sequencing of the NC and IN genes.</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -7542,13 +7538,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Env, NC, IN</t>
+          <t>The paper mentions using Sanger sequencing for some methods.</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -7563,17 +7563,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>The paper does not mention whether samples were cloned prior to sequencing.</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -7588,17 +7588,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>RT, IN, NC, Env</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Peripheral blood mononuclear cells (PBMCs) were sequenced.</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>The paper discusses integrase strand transfer inhibitors (INSTIs).</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -7638,17 +7638,13 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>The drug mentioned in the context of the study is dolutegravir (DTG).</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -7658,12 +7654,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7673,7 +7669,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Yes, the paper reports HIV sequences from patient samples. Specifically, the HIV-1 gag-protease DNA fragment from a total of 24 patient samples was cloned into pXXLAI, including samples with non-B HIV-1 subtypes and HIV-1 B subtype.</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -7683,22 +7679,18 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>The paper reports sequencing of the HIV-1 gag-protease DNA fragment and the capsid and reverse transcriptase sequences from selected viruses to determine the presence of resistance mutations.</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -7708,18 +7700,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr"/>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Yes, the paper mentions that the patient plasma samples were obtained from various clinical studies such as GS-US-380-1490, GS-US-292-0104, GS-US-200-4334, and GS-US-200-4625.</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -7734,7 +7730,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7744,7 +7740,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV-1 sequences from patient plasma samples.</t>
+          <t>The paper states that HIV-1 sequences from a total of 24 patient samples were analyzed and included in the study.</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -7759,13 +7755,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the capsid and reverse transcriptase genes.</t>
+          <t>The study did not mention the specific drug classes received by individuals before sample sequencing, specifically mentioned that the participants were treatment naive.</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -7780,17 +7780,13 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>The paper mentions the use of population sequencing.</t>
+          <t>The study did not mention the specific drugs received by individuals before sample sequencing, specifically mentioned that the participants were treatment naive.</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -7800,22 +7796,18 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>The paper sequenced viral supernatants obtained from patient isolates.</t>
+          <t>The paper reports sequencing of the protease, reverse transcriptase, and integrase genes.</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -7825,22 +7817,22 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>223</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Yes, the paper mentions that the patient plasma samples were obtained from clinical studies.</t>
+          <t>The paper does not specify the countries from which the sequenced samples were obtained.</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -7850,22 +7842,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>The paper involved 24 patient samples for HIV sequencing.</t>
+          <t>The sequenced samples were obtained from 1997 to 2019.</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -7880,17 +7872,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1997-2019</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>GenBank accession numbers not provided.</t>
+          <t>The paper used proviral DNA genotyping of PR/RT/IN using GenoSure Archive (Monogram Biosciences, CA, USA).</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -7905,13 +7897,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Protease (PR), reverse transcriptase (RT), and integrase (IN) were sequenced.</t>
+          <t>The paper sequenced whole blood samples.</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -7926,17 +7922,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>PBMC (Whole blood OK)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>The specific countries are not mentioned in the paper.</t>
+          <t>Yes, the patients were part of clinical trials.</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -7951,17 +7947,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Samples were collected from March 1997 to March 2019.</t>
+          <t>The paper obtained samples from 241 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -7976,17 +7972,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>1997-2019</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>The GenoSure Archive method was used for sequencing.</t>
+          <t>The individuals in the study received NRTIs, INSTIs, and PIs before sample sequencing.</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -8001,17 +7997,17 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Whole blood and proviral DNA samples were sequenced.</t>
+          <t>The individuals in the study received bictegravir, emtricitabine, and tenofovir alafenamide before sample sequencing.</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -8021,22 +8017,18 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>PBMC (Whole blood OK)</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Yes, the patients were part of clinical trials.</t>
+          <t>The paper reports sequencing of the whole genome of HIV-1.</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -8046,22 +8038,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>241 individuals had samples obtained for HIV sequencing.</t>
+          <t>The sequenced samples were obtained from the United Kingdom.</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -8071,22 +8063,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, and INSTI were received before sample sequencing.</t>
+          <t>The sequenced samples were obtained between 2015 and 2021.</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -8096,22 +8088,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>2015-2021</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Bictegravir/emtricitabine/tenofovir alafenamide were received prior to sample sequencing.</t>
+          <t>The complete genomic sequencing of HIV was performed using a sequence capture method and assembled into consensus whole genomes using Genomancer.</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -8126,13 +8118,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the entire HIV genome, including nonintegrase genes.</t>
+          <t>The samples sequenced were from patients with recently acquired HIV-1.</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -8147,17 +8143,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from the United Kingdom.</t>
+          <t>A total of 1182 individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -8172,17 +8168,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained between 2015 and 2021.</t>
+          <t>Individuals in the study had not received any ARV drugs before sample sequencing.</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -8197,17 +8193,13 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>2015-2021</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>The paper used a sequence capture method and the short read data were assembled into consensus whole genomes using Canu Genomancer.</t>
+          <t>Individuals in the study had not received any ARV drugs before sample sequencing.</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -8222,17 +8214,13 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>Yes, the sequences were made publicly available.</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -8242,22 +8230,22 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes (Only past sequences)</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Yes, the paper mentions sequences obtained from individuals with virological failure.</t>
+          <t>No, the paper does not report HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -8267,22 +8255,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>249 (uncertain)</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>A total of 1182 people had available WGS data between 2015 and 2021.</t>
+          <t>The paper mentions Italy as the country of the study.</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -8292,22 +8280,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Yes, the paper reports sequences from individuals who had previously received ARV drugs.</t>
+          <t>The paper does not specify the years from which the sequenced samples were obtained.</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -8317,22 +8305,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>The individuals in the study received integrase strand transfer inhibitors (INSTIs) before sample sequencing.</t>
+          <t>The paper does not specify the type of samples that were sequenced.</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -8342,18 +8330,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>The individuals in the study received raltegravir, dolutegravir, elvitegravir, or bictegravir before sample sequencing.</t>
+          <t>Yes, the paper discusses virological failure in individuals on treatment regimens.</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -8368,17 +8360,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>No, the study does not report HIV sequences from patient samples.</t>
+          <t>The paper does not specify the number of individuals from whom samples were obtained for sequencing.</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -8393,17 +8385,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>249 (uncertain)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>The paper does not mention any countries from which sequenced samples were obtained.</t>
+          <t>Yes, the paper includes individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -8418,17 +8410,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>The paper does not specify the years from which sequenced samples were obtained.</t>
+          <t>The paper mentions integrase inhibitors and protease inhibitors.</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -8443,17 +8435,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>PI, INSTI, NRTI (presumably)</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>The paper does not detail any sequencing methods.</t>
+          <t>The paper specifically mentions dolutegravir and darunavir.</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -8463,22 +8455,18 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>PR, RT, IN (presumably)</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples sequenced.</t>
+          <t>The integrase region was sequenced, and mutations in the reverse transcriptase and protease regions were also analyzed when available.</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -8488,22 +8476,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>The paper does not specify the number of individuals from whom samples were obtained for sequencing.</t>
+          <t>The sequenced samples were obtained from Mozambique.</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -8513,22 +8501,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>The paper does not specify drug classes received by individuals prior to sequencing.</t>
+          <t>The sequenced samples were obtained between 2023 and 2024.</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -8538,22 +8526,22 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
+          <t>2022-2024</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>The paper does not provide specific drug names received by individuals before sequencing.</t>
+          <t>The Sanger method was used for sequencing.</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -8568,17 +8556,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT,IN</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates were not provided in the paper.</t>
+          <t>Plasma samples were sequenced.</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -8593,13 +8581,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>The integrase gene was sequenced, and when available, mutations in the reverse transcriptase and protease regions were also analyzed.</t>
+          <t>Yes, sequences were obtained from individuals with virological failure on a treatment regimen.</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -8614,17 +8606,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Mozambique.</t>
+          <t>28 individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -8639,17 +8631,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>The samples were obtained from 2023 to 2024.</t>
+          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -8664,17 +8656,17 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Sanger sequencing was used for HIV gene sequencing.</t>
+          <t>Individuals received NRTIs, NNRTIs, and protease inhibitors.</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -8689,17 +8681,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>RT,IN</t>
+          <t>NRTI,NNRTI,INSTI</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>Specific drugs were not detailed, but DTG-based regimens were used.</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -8709,22 +8701,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41029850</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes (some)</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Yes, the study focused on individuals with confirmed virological failure on DTG-based ART.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates are: PQ893197, PQ893192, OQ985810, OR259747, and PQ893191.</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -8734,22 +8726,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41029850</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PQ893197, PQ893192, OQ985810, OR259747 and PQ893191 &amp; submission ID: 2961867)</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>28 individuals had samples obtained for HIV sequencing.</t>
+          <t>The HIV genes reported to have been sequenced are the protease (PR) and reverse transcriptase (RT) genes.</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -8759,22 +8751,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41029850</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>203</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Yes, the study reported sequences from individuals who had previously received ARV drugs.</t>
+          <t>The sequenced samples were obtained from Cameroon.</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -8784,22 +8776,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41029850</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Individuals received NRTIs, NNRTIs, and PIs before sample sequencing.</t>
+          <t>The sequenced samples were obtained from January 2022 to April 2023.</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -8809,22 +8801,22 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41029850</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI,INSTI</t>
+          <t>2022-2023</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Specific drugs like Tenofovir, Lamivudine, Emtricitabine, Efavirenz were received by individuals in the study before sample sequencing.</t>
+          <t>The method used for sequencing was Sanger sequencing.</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -8839,17 +8831,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Yes (some)</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>PQ893197, PQ893192, OQ985810, OQ259747, and PQ893191.</t>
+          <t>The sequenced samples were plasma samples with viral load ≥ 1000 copies/ml.</t>
         </is>
       </c>
       <c r="E342" t="n">
@@ -8864,17 +8856,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>PQ893197, PQ893192, OQ985810, OR259747 and PQ893191 &amp; submission ID: 2961867)</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>HIV-1 protease and reverse-transcriptase genes were sequenced.</t>
+          <t>Yes, the study obtained sequences from individuals with virological failure on a treatment regimen.</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -8889,17 +8881,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Cameroon.</t>
+          <t>Samples were obtained from 203 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -8914,17 +8906,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>The samples were obtained from January 2022 to April 2023.</t>
+          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -8939,17 +8931,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Sanger sequencing was used for sequencing the samples.</t>
+          <t>Individuals in the study received NRTI, NNRTI, and PI/r drug classes before sample sequencing.</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -8964,17 +8956,17 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>Individuals in the study received AZT, 3TC, ABC, LPV/r, ATV/r, TDF, DTG, and EFV prior to sample sequencing.</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -8984,22 +8976,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>41029850</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure.</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -9009,22 +9001,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>41029850</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>203 individuals had samples obtained for HIV sequencing.</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="E349" t="n">
@@ -9034,22 +9026,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>41029850</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>Yes.</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -9059,12 +9051,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>41029850</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -9074,7 +9066,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, and PIs were received before sample sequencing.</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="E351" t="n">
@@ -9084,22 +9076,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>41029850</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Drugs received included ABC, 3TC, EFV, NVP, AZT, DTG, ATV/r, LPV/r, TDF.</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -9109,22 +9101,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>41029850</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>AZT, 3TC, ABC, TDF, EFV, NVP, ATV, RTV, LPV, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Yes, sequences were submitted to GenBank.</t>
+          <t>NRTIs, Integrase inhibitors.</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -9139,13 +9131,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr"/>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI, CAI</t>
+        </is>
+      </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>The paper mentions the sequencing of the HIV-1 capsid gene for resistance testing.</t>
+          <t>Emtricitabine, tenofovir alafenamide, lenacapavir, bictegravir.</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -9155,22 +9151,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from the USA and the Dominican Republic.</t>
+          <t>No, the study does not report new HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -9180,22 +9176,18 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>The samples were obtained between 22 November 2019 and 27 August 2020.</t>
+          <t>The paper reports sequencing of the protease, RT, and integrase genes.</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -9205,22 +9197,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>235</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>The study sequenced plasma samples from participants.</t>
+          <t>The sequenced samples were obtained from Uganda.</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -9230,22 +9222,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals who met virologic failure criteria.</t>
+          <t>The samples were obtained from 2018 to 2023.</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -9255,22 +9247,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>2018-2023</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Yes, the study was a clinical trial.</t>
+          <t>The paper does not specify the exact method used for sequencing.</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -9280,22 +9272,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>182 participants received at least one dose of study drug, and those who met virologic failure criteria were included in the resistance analysis population.</t>
+          <t>The paper does not specify the type of samples sequenced, such as plasma or PBMCs.</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -9305,22 +9297,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger (not stated)</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Participants received drugs from the NRTI, integrase inhibitor, and fusion inhibitor classes.</t>
+          <t>Yes, the paper reports sequences obtained from individuals with virological failure.</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -9330,22 +9322,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, CAI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Drugs received include lenacapavir, emtricitabine, tenofovir alafenamide, and bictegravir.</t>
+          <t>Samples were obtained from 235 individuals living with HIV.</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -9360,13 +9352,17 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>The paper discusses mutations in several HIV genes, including those conferring resistance.</t>
+          <t>Yes, the paper reports sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -9381,17 +9377,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Uganda.</t>
+          <t>Participants received NRTI, NNRTI, PI, or INSTI drug classes before sample sequencing.</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -9406,17 +9402,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>NRTI,NNRTI,PI, INSTI</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from 2018 to 2023.</t>
+          <t>Specific drugs received included ABC, AZT, D4T, TDF, DTG, DRV, ETR, LPV, and RAL.</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -9426,22 +9422,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>The paper does not specify the method used for sequencing.</t>
+          <t>The GenBank accession number for sequenced HIV isolates is PV187006.</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -9451,22 +9447,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>PV187006</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of clinical specimens sequenced.</t>
+          <t>The near full-length genome (NFLG) of HIV-1 was sequenced, covering multiple genes.</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -9476,22 +9472,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Sanger (not stated)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure.</t>
+          <t>The sequenced samples were obtained from China.</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -9501,22 +9497,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>The study involved 235 individuals who underwent HIV drug resistance testing.</t>
+          <t>The sequenced samples were obtained in 2023 and 2025.</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -9526,22 +9522,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>The sequencing method used was Sanger sequencing.</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -9551,12 +9547,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -9566,7 +9562,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Individuals received NRTI, NNRTI, PI, and INSTI drug classes before sample sequencing.</t>
+          <t>No, the samples were not cloned prior to sequencing.</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -9576,22 +9572,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI,PI, INSTI</t>
+          <t>Whole genome</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Specific drugs received included AZT, TDF, D4T, and TDF.</t>
+          <t>Plasma and whole-blood samples were sequenced.</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -9606,17 +9602,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>The GenBank accession number for the HIV isolate from individual 230794 is PV187006.</t>
+          <t>One individual had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -9631,17 +9627,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>PV187006</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>The sequenced genes include the near full-length genome (NFLG), specifically mentioning regions of vif and env genes, and the pol gene.</t>
+          <t>The individuals in the study had not received any drug classes before sample sequencing as they were ART-naive.</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -9656,17 +9652,13 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from China.</t>
+          <t>The individuals in the study had not received any drugs before sample sequencing as they were ART-naive.</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -9681,17 +9673,13 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from 2023 and 2025.</t>
+          <t>Yes, the sequences from the paper were made publicly available.</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -9701,22 +9689,18 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>The sequencing method used was Sanger sequencing.</t>
+          <t>HIV-1 protease was reported to have been sequenced.</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -9726,7 +9710,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -9736,12 +9720,12 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (site-directed mutants)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>No, samples were not cloned prior to sequencing.</t>
+          <t>The paper does not mention whether samples were cloned prior to sequencing.</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -9751,7 +9735,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -9761,12 +9745,12 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Whole genome</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>The sequenced samples included plasma and whole-blood samples.</t>
+          <t>The paper does not specify the type of samples that were sequenced.</t>
         </is>
       </c>
       <c r="E379" t="n">
@@ -9776,12 +9760,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -9791,7 +9775,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Samples were obtained from one individual for HIV sequencing.</t>
+          <t>The paper discusses the use of protease inhibitors, indicating the drug class received.</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -9801,22 +9785,18 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>The individuals in the study had not received any drugs before sample sequencing.</t>
+          <t>The paper specifically mentions darunavir as a drug used in the study.</t>
         </is>
       </c>
       <c r="E381" t="n">
@@ -9826,18 +9806,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr"/>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Yes (recombinant clones)</t>
+        </is>
+      </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>The individuals in the study had not received any drugs before sample sequencing.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates are PQ735970-PQ735985.</t>
         </is>
       </c>
       <c r="E382" t="n">
@@ -9847,18 +9831,22 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr"/>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>PQ735970–PQ735985</t>
+        </is>
+      </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Yes, the sequences were made publicly available.</t>
+          <t>The Pol region was reported to have been sequenced.</t>
         </is>
       </c>
       <c r="E383" t="n">
@@ -9868,22 +9856,22 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>The paper does not describe the sequencing method used.</t>
+          <t>The sequenced samples were obtained from China and the United States.</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -9893,22 +9881,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>The paper does not mention whether samples were cloned prior to sequencing.</t>
+          <t>The sequenced samples were obtained from 1978 to 2023.</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -9918,22 +9906,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples that were sequenced.</t>
+          <t>The study used Sanger sequencing.</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -9948,17 +9936,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Yes (recombinant clones)</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>The NCBI repository accession numbers for the AE/B recombinants are: PQ735970-PQ735985.</t>
+          <t>No HIV-1 samples from patients were sequenced in this study. The study was based on laboratory-reconstructed viruses, which differ from sequencing patient samples.</t>
         </is>
       </c>
       <c r="E387" t="n">
@@ -9973,17 +9961,13 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>PQ735970–PQ735985</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>The Pol region sequences were analyzed.</t>
+          <t>Yes, the sequences were made publicly available.</t>
         </is>
       </c>
       <c r="E388" t="n">
@@ -9993,22 +9977,22 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>The samples were obtained from China and the United States.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates are PP280627 to PP280757.</t>
         </is>
       </c>
       <c r="E389" t="n">
@@ -10018,22 +10002,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>PP280627- PP280757</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>The samples were obtained from 1978 to 2023.</t>
+          <t>The partial reverse transcriptase (RT) gene was sequenced.</t>
         </is>
       </c>
       <c r="E390" t="n">
@@ -10043,22 +10027,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>237</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Sanger sequencing was used.</t>
+          <t>The sequenced samples were obtained from Senegal.</t>
         </is>
       </c>
       <c r="E391" t="n">
@@ -10068,22 +10052,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>The samples were likely plasmid-based recombinant viruses.</t>
+          <t>The sequenced samples were obtained between 2017 and 2018.</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -10093,18 +10077,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2017-2018</t>
+        </is>
+      </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Yes, the sequences were made publicly available in the NCBI repository.</t>
+          <t>Sequencing was performed using the Big Dye Terminator v3.1 method and ABI 3100 Avant sequencer.</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -10119,17 +10107,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are PP280627 to PP280757.</t>
+          <t>Both dried blood spots (DBS) and plasma samples were sequenced.</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -10144,17 +10132,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>PP280627- PP280757</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>The partial reverse transcriptase (RT) gene was sequenced.</t>
+          <t>Samples were obtained from 331 antiretroviral therapy-naive patients.</t>
         </is>
       </c>
       <c r="E395" t="n">
@@ -10169,17 +10157,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Senegal.</t>
+          <t>The individuals were antiretroviral therapy-naive, so no drug classes were received before sampling.</t>
         </is>
       </c>
       <c r="E396" t="n">
@@ -10194,17 +10182,13 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained between 2017 and 2018.</t>
+          <t>The individuals were antiretroviral therapy-naive, so no specific drugs were received before sampling.</t>
         </is>
       </c>
       <c r="E397" t="n">
@@ -10219,17 +10203,13 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>2017-2018</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer were used for sequencing.</t>
+          <t>Yes, the sequences were deposited in the National Institutes of Health GenBank database.</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -10239,22 +10219,22 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Dried blood spots (DBS) and whole blood samples were sequenced.</t>
+          <t>Yes, the paper reports in vitro drug susceptibility data based on Sanger sequencing results.</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -10264,22 +10244,18 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Samples were obtained from 251 individuals for HIV sequencing.</t>
+          <t>The paper mentions sequencing for drug resistance mutations primarily in the reverse transcriptase, protease, and integrase genes.</t>
         </is>
       </c>
       <c r="E400" t="n">
@@ -10289,22 +10265,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>All participants were ART-naive, so they had not received any drugs before sample sequencing.</t>
+          <t>The sequenced samples were obtained from Uganda.</t>
         </is>
       </c>
       <c r="E401" t="n">
@@ -10314,18 +10290,22 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr"/>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>All participants were ART-naive, so they had not received any drugs before sample sequencing.</t>
+          <t>The sequenced samples were obtained between January and November 2021.</t>
         </is>
       </c>
       <c r="E402" t="n">
@@ -10335,18 +10315,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Yes, the sequences were deposited in the GenBank database.</t>
+          <t>The paper used Sanger sequencing technology for sequencing.</t>
         </is>
       </c>
       <c r="E403" t="n">
@@ -10361,17 +10345,17 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT, PR, IN</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Yes, the paper reports in vitro drug susceptibility data.</t>
+          <t>Plasma samples were sequenced.</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -10386,13 +10370,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>The study focused on sequences relevant to drug resistance, particularly in the context of integrase inhibitors, protease inhibitors, NRTIs, NNRTIs, and integrase inhibitors.</t>
+          <t>Yes, the paper reports sequences obtained from individuals with virological failure on their treatment regimen.</t>
         </is>
       </c>
       <c r="E405" t="n">
@@ -10407,17 +10395,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Uganda.</t>
+          <t>Samples were obtained from 333 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -10432,17 +10420,17 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>The samples were obtained between January and November 2021.</t>
+          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -10457,17 +10445,17 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Sanger sequencing method was used for sequencing.</t>
+          <t>Individuals received drugs from the NRTI, NNRTI, PI, and INSTI classes before sample sequencing.</t>
         </is>
       </c>
       <c r="E408" t="n">
@@ -10482,17 +10470,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>RT, PR, IN</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>Drugs received included Dolutegravir, Abacavir, Zidovudine, Tenofovir, Lopinavir, Lamivudine, Darunavir, Efavirenz, and Nevirapine.</t>
         </is>
       </c>
       <c r="E409" t="n">
@@ -10502,22 +10490,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates are not provided in the paper.</t>
         </is>
       </c>
       <c r="E410" t="n">
@@ -10527,22 +10515,18 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Samples were obtained from 333 individuals for HIV sequencing.</t>
+          <t>The HIV genes sequenced include capsid, protease, reverse transcriptase, and integrase.</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -10552,22 +10536,22 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>The sequenced samples were obtained from multiple countries, including South Africa.</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -10577,22 +10561,22 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Individuals received NRTIs, NNRTIs, PIs, and INSTIs before sample sequencing.</t>
+          <t>The specific years from which the sequenced samples were obtained are not provided in the paper.</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -10602,22 +10586,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>The received drugs included DTG, ABC, AZT, TDF, LPV, 3TC, DRV, EFV, NVP, and ATV.</t>
+          <t>Next-generation sequencing (NGS) was used for sequencing.</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -10632,13 +10616,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr"/>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>The HIV genes sequenced include capsid, protease, reverse transcriptase, and integrase.</t>
+          <t>No, samples were not cloned prior to sequencing.</t>
         </is>
       </c>
       <c r="E415" t="n">
@@ -10653,17 +10641,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>RT,PR,IN,CA</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>The paper mentions samples from South Africa and other unspecified countries.</t>
+          <t>Plasma samples were sequenced.</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -10678,17 +10666,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>The specific years from which samples were obtained are not provided in the paper.</t>
+          <t>Yes, sequences were obtained from individuals with virological failure.</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -10703,17 +10691,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Next-generation sequencing (NGS) was used for sequencing.</t>
+          <t>Yes, the patients were part of clinical trials.</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -10728,17 +10716,17 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>Yes (PrEP)</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>No, samples were not cloned prior to sequencing.</t>
+          <t>A total of 53 individuals had samples obtained for HIV sequencing in the resistance analysis population (RAP).</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -10753,17 +10741,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>RT,PR,IN,CA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Plasma samples were collected for sequencing.</t>
+          <t>Participants received NRTIs and INSTIs before sample sequencing.</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -10778,17 +10766,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>NRTI, CAI</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure.</t>
+          <t>Drugs received include tenofovir disoproxil fumarate (TDF), lamivudine (3TC), and dolutegravir (DTG).</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -10798,22 +10786,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Yes, the patients were part of clinical trials (PURPOSE 1 and 2).</t>
+          <t>The paper reports sequencing of the pol gene, including PR, RT, and IN regions.</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -10823,22 +10811,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Yes (PrEP)</t>
+          <t>0 (Review paper)</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Samples were obtained from a total of 54 individuals in the PURPOSE 1 and PURPOSE 2 trials.</t>
+          <t>The sequenced samples were obtained from Kenya, Uganda, Tanzania, and Ethiopia.</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -10848,22 +10836,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>NRTIs and INSTIs were received by individuals in the study.</t>
+          <t>The sequenced samples were obtained between 2015 and 2025.</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -10873,22 +10861,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>NRTI, CAI</t>
+          <t>Not available (deposited 2015-2025)</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Specific drugs mentioned include emtricitabine, tenofovir, and dolutegravir, lamivudine.</t>
+          <t>The specific method used for sequencing is not mentioned in the paper.</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -10903,17 +10891,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>The HIV genes sequenced include those coding for Protease (PR), Reverse Transcriptase (RT), and Integrase (IN).</t>
+          <t>The paper does not specify the type of clinical specimens sequenced.</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -10928,17 +10916,17 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>0 (Review paper)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Kenya, Uganda, Tanzania, and Ethiopia.</t>
+          <t>The paper does not specify the number of individuals from whom samples were obtained for sequencing.</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -10953,17 +10941,17 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from the years 2015 to 2025.</t>
+          <t>The paper does not specify the drug classes received by individuals before sample sequencing.</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -10978,95 +10966,20 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of clinical specimens sequenced, whether they were plasma, PBMCs or other types.</t>
+          <t>The paper does not specify the drugs received by individuals before sample sequencing.</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>The paper does not specify the number of individuals from whom samples were obtained for sequencing.</t>
-        </is>
-      </c>
-      <c r="E430" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>The paper does not provide information on the drug classes received by individuals prior to sequencing.</t>
-        </is>
-      </c>
-      <c r="E431" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>The paper does not specify which drugs were received by individuals prior to sequencing.</t>
-        </is>
-      </c>
-      <c r="E432" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E429"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,8 +744,10 @@
       <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1011,8 +1013,10 @@
       <c r="C24" t="n">
         <v>51</v>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1157,8 +1161,10 @@
       <c r="C30" t="n">
         <v>6</v>
       </c>
-      <c r="D30" t="n">
-        <v>35</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1330,8 +1336,10 @@
           <t>120 * 76% = 95, or 120 or 129</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>6</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1451,8 +1459,10 @@
       <c r="C42" t="n">
         <v>14</v>
       </c>
-      <c r="D42" t="n">
-        <v>0</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1649,8 +1659,10 @@
           <t>8 and 10</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1045</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1747,8 +1759,10 @@
           <t>62 or 3</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>0</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2243,8 +2257,10 @@
       <c r="C74" t="n">
         <v>1651</v>
       </c>
-      <c r="D74" t="n">
-        <v>0</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2689,8 +2705,10 @@
       <c r="C92" t="n">
         <v>1</v>
       </c>
-      <c r="D92" t="n">
-        <v>0</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -2787,8 +2805,10 @@
           <t>70 or 79</t>
         </is>
       </c>
-      <c r="D96" t="n">
-        <v>0</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -2908,8 +2928,10 @@
       <c r="C101" t="n">
         <v>551</v>
       </c>
-      <c r="D101" t="n">
-        <v>0</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -3554,8 +3576,10 @@
       <c r="C127" t="n">
         <v>33</v>
       </c>
-      <c r="D127" t="n">
-        <v>600</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -3750,8 +3774,10 @@
       <c r="C135" t="n">
         <v>5</v>
       </c>
-      <c r="D135" t="n">
-        <v>0</v>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -3871,8 +3897,10 @@
       <c r="C140" t="n">
         <v>0</v>
       </c>
-      <c r="D140" t="n">
-        <v>146</v>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -4186,17 +4214,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>227</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are PV008448-PV008641, PV407014-PV407203, and PV419497-PV419583.</t>
+          <t>Samples were obtained from 488 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4206,22 +4232,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>PV008448-PV008641, PV407014-PV407203,  PV419497-PV419583</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>47</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>The HIV genes sequenced were integrase (IN) and protease/reverse transcriptase (PR/RT) regions.</t>
+          <t>Samples were obtained from 54 participants who were diagnosed with HIV during the trial.</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4231,7 +4255,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4241,12 +4265,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, and Zimbabwe.</t>
+          <t>The sequenced samples were obtained from England, as the trial was conducted across Sexual Health Services in England.</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4256,22 +4280,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cameroon, Cote d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained between June 2022 and December 2024.</t>
+          <t>Yes, the patients were part of the PrEP Impact trial.</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4281,22 +4305,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>TDF, FTC</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sanger sequencing was used for sequencing.</t>
+          <t>Specific drugs received included TDF, FTC, DTG, DRV, 3TC, ABC, and RAL, reflecting the treatments received prior to HIV sequencing.</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4306,22 +4330,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>2006-2024</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Both plasma and dried blood spots (DBS) were sequenced.</t>
+          <t>The sequenced samples were obtained from 2022-2024.</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4331,12 +4355,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4346,7 +4370,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure on a treatment regimen.</t>
+          <t>Next generation sequencing was used for genotypic resistance tests.</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4356,22 +4380,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>234 individuals had samples obtained for HIV sequencing.</t>
+          <t>Plasma RNA and proviral DNA from PBMCs were sequenced.</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4381,12 +4405,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4396,7 +4420,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>Yes, the patient was enrolled in the Swiss HIV Cohort Study and participated in the TMC-125 trial.</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4406,22 +4430,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Individuals received Integrase Strand Transfer Inhibitors (INSTIs), Nucleos(t)ide Reverse Transcriptase Inhibitors (NRTIs), and Protease Inhibitors (PIs) before sample sequencing.</t>
+          <t>Zidovudine (AZT), ritonavir (RTV), didanosine (ddI), abacavir (ABC), tenofovir disoproxil (TDF), lopinavir (LPV), etravirine (ETR), atazanavir (ATV), raltegravir (RAL), emtricitabine (FTC), dolutegravir (DTG), darunavir (DRV), and bictegravir (BIC).</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4431,22 +4455,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>TDF, 3TC, DTG, RAL</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1677</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Yes, the sequences were made publicly available.</t>
+          <t>Samples from 1667 individuals were included in the mutation analysis.</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4456,22 +4478,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>47</t>
+          <t xml:space="preserve">Sanger  </t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>The samples were obtained from England.</t>
+          <t>The paper used a PCR-based method for sequencing the HIV-1 pol gene fragments.</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4481,22 +4503,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>The samples were obtained between October 13, 2017, and July 12, 2020.</t>
+          <t>The paper mentions that plasma HIV-1 RNA samples were sequenced.</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4506,22 +4528,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40490983</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2017-2020</t>
+          <t>AZT, 3TC, TDF, ABC, EFV, NVP, LPV, RTV, ATV (RTV is for boosting)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>The paper does not specify the sequencing method used.</t>
+          <t>The paper mentioned specific drugs such as atazanavir/ritonavir and lopinavir/ritonavir received prior to sequencing. The NRTIs lamivudine, zidovudine, and tenofovir were received before sequencing</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4531,22 +4553,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>RT,IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples sequenced.</t>
+          <t>The GenBank accession numbers for the sequenced HIV isolates are not provided in the text.</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4556,12 +4578,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4571,7 +4593,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Yes, the paper describes a clinical trial.</t>
+          <t>The type of samples sequenced were plasma or serum from patients.</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4581,22 +4603,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Yes (PrEP)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Samples were obtained from 54 participants who were diagnosed with HIV during the trial.</t>
+          <t>The study included individuals who were ART-naïve at the time of sample sequencing, so they had not received any drug classes before sequencing.</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4606,22 +4628,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>The paper reports on PrEP usage but does not detail other drug classes received before sampling.</t>
+          <t>The study included individuals who were ART-naïve at the time of sample sequencing, so they had not received any drugs before sequencing.</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4631,22 +4653,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>The individuals in the study received oral PrEP consisting of tenofovir disoproxil fumarate and emtricitabine.</t>
+          <t>The sequencing method used was the ViroSeq Genotyping System.</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4656,18 +4678,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the protease and reverse transcriptase genes. It also discusses mutations in the integrase gene, indicating that the integrase gene was analyzed for resistance mutations.</t>
+          <t>The sequenced samples were clinical specimens from mother-child pairs with confirmed vertical transmission of HIV-1.</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4677,22 +4703,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Switzerland, as indicated by the mention of the Swiss HIV Cohort Study and the biobank from which the samples were sourced.</t>
+          <t>Individuals in the study received zidovudine (ZDV), lamivudine (3TC), nevirapine (NVP), lopinavir/ritonavir, and efavirenz (EFV) before sample sequencing.</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4702,22 +4728,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40713598</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from various years, with specific dates mentioned in the context of genotypic resistance tests. Key dates include 2006, 2022, 2023, and 2024.</t>
+          <t>HIV drug resistance (HIVDR) was retrospectively characterized among 20 children and adolescents with HIV with virologic failure on non-nucleoside reverse transcriptase inhibitor (NNRTI)-based therapy, and virologic response in those switched to dolutegravir (DTG)-based therapy described.</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -4727,22 +4753,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2006-2024</t>
+          <t>AZT, ABC, 3TC, TDF, ATV, LPV, RTV, DTG</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>The paper mentions the use of next-generation sequencing (NGS) for genotypic resistance testing. This indicates that NGS was the method employed for sequencing the HIV genomes.</t>
+          <t>The study involved participants on various ART regimens including TDF/3TC/DTG, AZT/3TC/DTG, ABC/3TC/DTG, ABC/3TC/LPVr, TDF/3TC/ATVr, AZT/3TC/ATVr, and others before sample sequencing.</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4752,22 +4778,20 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>20</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Yes, the paper discusses sequences obtained from an individual with virological failure on a treatment regimen. It describes the emergence of resistance mutations following virological failure on a quadruple regimen including bictegravir and doravirine.</t>
+          <t>Samples were obtained from 2028 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4777,22 +4801,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Yes, the paper mentions that the patient was enrolled in the Swiss HIV Cohort Study and participated in the TMC-125 trial, indicating that some aspects of the patient's treatment were part of a clinical trial.</t>
+          <t>The study used population sequencing level.</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4802,22 +4826,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>The paper focuses on a single case study of one individual, indicating that samples were obtained from this one patient for HIV sequencing.</t>
+          <t>The paper mentions that whole blood samples were used for sequencing.</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4827,22 +4851,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from an individual who had previously received multiple antiretroviral (ARV) drugs. The patient described in the study is treatment-experienced and had received various ARV drugs over the years.</t>
+          <t>Participants received Tenofovir, INSTIs, NNRTIs, and PIs before sample sequencing.</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4852,22 +4876,20 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40839365</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>212</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>The individual in the study received NRTIs, NNRTIs, PIs, and INSTIs before sample sequencing. The paper discusses the evolution of resistance across these drug classes over time.</t>
+          <t>Samples were obtained from 213 individuals with confirmed virologic failure.</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -4877,22 +4899,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>7 (Uncertain)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>The individual in the study received a variety of ARV drugs over the years, including zidovudine, ritonavir, didanosine, abacavir, tenofovir disoproxil, lopinavir/ritonavir, etravirine, raltegravir, tenofovir alafenamide, emtricitabine, elvitegravir, darunavir, bictegravir, and doravirine.</t>
+          <t>The paper mentions resistance testing data for 22 participants.</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4902,18 +4924,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>The study sequenced the protease and reverse-transcriptase regions of the HIV-1 pol gene.</t>
+          <t>The paper does not detail the specific method used for sequencing.</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4923,22 +4949,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Argentina.</t>
+          <t>The paper does not specify the type of samples that were sequenced.</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -4948,22 +4974,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>The samples were collected between 2017 and 2021.</t>
+          <t>Yes the paper reports HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -4973,22 +4999,20 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>2017-2021</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>The sequencing was performed using an Applied Biosystems/Hitachi 3500 Genetic Analyzer.</t>
+          <t>A total of 9685 individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -4998,22 +5022,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>RT,PR</t>
+          <t>2004-2021</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>The sequenced samples were obtained from studies published up to 2024, covering various years including 2005-2021.</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5023,22 +5047,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Samples from 1667 individuals were analyzed.</t>
+          <t>The paper reports sequencing of the RT and integrase gene.</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5048,22 +5072,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are not reported in the provided text.</t>
+          <t>The paper does not specify the exact sequencing method used.</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5073,18 +5097,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>The genes sequenced include protease and reverse transcriptase as indicated by the resistance mutations analyzed in those genes.</t>
+          <t>The paper does not specify the type of clinical samples sequenced.</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5094,22 +5122,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Kenya, specifically through the Academic Model Providing Access to Healthcare in western Kenya.</t>
+          <t>The drugs received by individuals in the study include TDF, 3TC, DTG, FTC, AZT, and LPV/r.</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5119,22 +5147,20 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1048</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from 2011 to 2021.</t>
+          <t>Samples were obtained from 1,260 individuals.</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5144,22 +5170,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2011-2021</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Sanger sequencing was used for sequencing the HIV samples.</t>
+          <t>There were no GenBank accession numbers.</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5169,22 +5195,20 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Plasma HIV-1 RNA samples were sequenced.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -5194,22 +5218,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Yes, the sequences were obtained from individuals with virological failure on a treatment regimen.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5219,22 +5243,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>A total of 187 individuals had samples obtained for HIV sequencing.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5244,22 +5268,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger, NGS</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5269,22 +5293,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Individuals received NRTI, NNRTI, and PI drug classes before sample sequencing; dual-class and triple-class resistance were also reported</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5294,22 +5318,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>The drugs received included atazanavir/ritonavir, lopinavir/ritonavir, lamivudine, tenofovir, nevirapine, and zidovudine, abacavir</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5319,22 +5343,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are not provided in the abstract or materials and methods of the paper.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5344,18 +5368,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>The genes sequenced include the envelope (env), gag, and pol proteins for genotyping and the protease, reverse transcriptase, and integrase genes for drug resistance analysis.</t>
+          <t>Yes, the paper reports HIV-1 sequences from patient plasma samples.</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5365,22 +5393,20 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from South Korea, with a significant portion from non-Korean individuals primarily from Asia and the Americas.</t>
+          <t>The paper involved 24 patient samples for HIV sequencing.</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5390,22 +5416,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from the years 2021 to 2024.</t>
+          <t>The paper mentions the use of population sequencing.</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5415,22 +5441,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Sanger sequencing was performed using in-house sequencing primers.</t>
+          <t>The paper sequenced viral supernatants obtained from patient isolates.</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5440,22 +5466,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Viral RNA was extracted from plasma or serum samples.</t>
+          <t>Yes, the paper mentions that the patient plasma samples were obtained from clinical studies.</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5465,22 +5491,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Samples were obtained from 487 individuals for HIV sequencing.</t>
+          <t>GenBank accession numbers not provided.</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5490,22 +5516,20 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>223</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The study included ART-naïve individuals, so no drug classes were received before sample sequencing.</t>
+          <t>241 individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5515,18 +5539,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The study included ART-naïve individuals, so no specific drugs were received before sample sequencing.</t>
+          <t>The specific countries are not mentioned in the paper.</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5536,22 +5564,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for the sequenced HIV isolates are PV526713-PV526742.</t>
+          <t>The GenoSure Archive method was used for sequencing.</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5561,22 +5589,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>PV526713-PV526742</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>The HIV pol region, specifically the protease and reverse transcriptase (PR/RT) genes, were sequenced.</t>
+          <t>No, the study included individuals without prior virological failure.</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5586,7 +5614,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5596,12 +5624,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Brazil.</t>
+          <t>The sequenced samples were obtained from the United Kingdom.</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5611,22 +5639,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Whole genome</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from 2007 to 2022.</t>
+          <t>The paper reports sequencing of the entire HIV genome, including nonintegrase genes.</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5636,7 +5664,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5646,12 +5674,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2007-2022</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>The ViroSeq Genotyping System was used for sequencing.</t>
+          <t>The paper used a sequence capture method and the short read data were assembled into consensus whole genomes using Canu Genomancer.</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5661,22 +5689,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Clinical samples from mother-child pairs with confirmed vertical transmission of HIV-1 were sequenced.</t>
+          <t>Yes, the paper mentions sequences obtained from individuals with virological failure.</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5686,22 +5714,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Yes, some mothers in the study had virological failure and required genotyping.</t>
+          <t>Yes, the paper reports sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5711,22 +5739,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Samples were obtained from 15 mother-child pairs, totaling 30 individuals.</t>
+          <t>The individuals in the study received integrase strand transfer inhibitors (INSTIs) before sample sequencing.</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5736,22 +5764,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Yes, the paper includes mothers who had previously received ARV drugs.</t>
+          <t>The individuals in the study received raltegravir, dolutegravir, elvitegravir, or bictegravir before sample sequencing.</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5761,22 +5789,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (Only past sequences)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Individuals in the study received drugs from the NRTI and NNRTI classes.</t>
+          <t>No, the study does not report HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -5786,22 +5814,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>249 (uncertain)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Individuals received zidovudine (ZDV), lamivudine (3TC), nevirapine (NVP), lopinavir/ritonavir, and efavirenz (EFV).</t>
+          <t>The paper does not specify the number of individuals from whom samples were obtained for sequencing.</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5811,22 +5839,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Yes, the GenBank accession numbers provided indicate that the sequences were made publicly available.</t>
+          <t>The paper does not mention any countries from which sequenced samples were obtained.</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5836,22 +5864,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers are not provided in the content of the paper. The study did not mention any accession numbers for the sequenced HIV isolates.</t>
+          <t>The paper does not report sequencing of specific HIV genes.</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5861,18 +5889,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr"/>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>The HIV-1 pol gene was sequenced, encompassing the protease (PR) and reverse transcriptase (RT) regions.</t>
+          <t>The paper does not detail any sequencing methods.</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5882,22 +5914,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Ghana, specifically from the Pediatric HIV/AIDS Care Program at Korle-Bu Teaching Hospital in Ghana.</t>
+          <t>The paper does not specify the type of samples sequenced.</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5907,22 +5939,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>The specific years from which the sequenced samples were obtained are not mentioned in the paper.</t>
+          <t>The paper does not mention any sequences obtained from individuals with virological failure.</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5932,22 +5964,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Next-generation sequencing (NGS) was conducted on the Illumina MiSeq platform.</t>
+          <t>The paper does not report HIV sequences from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -5957,22 +5989,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>PI, INSTI, NRTI (presumably)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Frozen plasma samples were used for sequencing.</t>
+          <t>The paper does not specify drug classes received by individuals prior to sequencing.</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -5982,22 +6014,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>DTG, DRV/r</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Yes, the paper reports sequences obtained from individuals with virological failure on a treatment regimen. It specifically focuses on children and adolescents with virologic failure on NNRTI-based therapy.</t>
+          <t>The paper does not provide specific drug names received by individuals before sequencing.</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6007,22 +6039,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Samples were attempted from 96 individuals with HIV-1 RNA &gt;1,000 copies/ml, but 20 samples were successfully amplified and sequenced.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates were not provided in the paper.</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6032,22 +6064,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2022-2024</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs. It discusses resistance in children and adolescents on NNRTI-based antiretroviral therapy.</t>
+          <t>The samples were obtained from 2023 to 2024.</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6057,22 +6089,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DTG (no other ARVs specified)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Individuals in the study received non-nucleoside reverse transcriptase inhibitors (NNRTIs) and nucleoside reverse transcriptase inhibitors (NRTIs) before sample sequencing.</t>
+          <t>Specific drugs like Tenofovir, Lamivudine, Emtricitabine, Efavirenz were received by individuals in the study before sample sequencing.</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6082,22 +6114,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>41029850</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t xml:space="preserve">PQ893197, PQ893192, OQ985810, OR259747 and PQ893191 &amp; submission ID: 2961867) </t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Specific drugs received by individuals included nevirapine, efavirenz, lamivudine, tenofovir, abacavir, and zidovudine before sample sequencing.</t>
+          <t>PQ893197, PQ893192, OQ985810, OQ259747, and PQ893191.</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6107,22 +6139,20 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>10</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>No, the paper does not report HIV sequences from patient samples.</t>
+          <t>182 participants received at least one dose of study drug, and those who met virologic failure criteria were included in the resistance analysis population.</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6132,7 +6162,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6142,12 +6172,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>The paper does not mention sequenced samples from any country.</t>
+          <t>The sequenced samples were obtained from the USA and the Dominican Republic.</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6157,7 +6187,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6167,12 +6197,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>The paper does not provide information on the years from which sequenced samples were obtained.</t>
+          <t>The samples were obtained between 22 November 2019 and 27 August 2020.</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6182,7 +6212,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6192,12 +6222,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>The study used Sanger sequencing or Next Generation Sequencing.</t>
+          <t>The paper does not specify the exact sequencing method used.</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -6207,22 +6237,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>The study used plasma or dried blood spot (DBS) samples for sequencing.</t>
+          <t>The paper discusses mutations in several HIV genes, including those conferring resistance.</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -6232,22 +6262,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Yes, the paper reports sequences from individuals with virological failure.</t>
+          <t>Specific drugs received included AZT, TDF, D4T, and TDF.</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -6257,12 +6287,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6272,7 +6302,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>295 individuals had samples obtained for HIV sequencing.</t>
+          <t>No, samples were not cloned prior to sequencing.</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6282,22 +6312,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Whole genome</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Yes, the paper includes participants who had previously received ARV drugs.</t>
+          <t>The sequenced genes include the near full-length genome (NFLG), specifically mentioning regions of vif and env genes, and the pol gene.</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6307,7 +6337,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6317,12 +6347,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Individuals received NRTIs, NNRTIs, PIs, and INSTIs before sample sequencing.</t>
+          <t>The individuals in the study had not received any drugs before sample sequencing.</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -6332,7 +6362,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6342,12 +6372,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Drugs received included Abacavir, Lamivudine, Zidovudine, Tenofovir, Dolutegravir, Atazanavir, Lopinavir, and Darunavir.</t>
+          <t>The individuals in the study had not received any drugs before sample sequencing.</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -6357,18 +6387,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Yes (site-directed mutants)</t>
+        </is>
+      </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>The HIV genes reported to have been sequenced include protease (PR), reverse transcriptase (RT), and integrase (IN).</t>
+          <t>The paper does not mention whether samples were cloned prior to sequencing.</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -6378,22 +6412,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>The paper does not specify the countries from which the sequenced samples were obtained.</t>
+          <t>The paper does not report specific HIV genes that were sequenced.</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6403,7 +6437,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6413,12 +6447,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>The sequencing method used was next-generation sequencing (NGS).</t>
+          <t>The paper does not describe the sequencing method used.</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6428,22 +6462,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Whole blood samples were sequenced for proviral DNA.</t>
+          <t>The samples were obtained from China and the United States.</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6453,22 +6487,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Yes, the patients were part of Phase 2/3/3b clinical trials.</t>
+          <t>The samples were obtained from 1978 to 2023.</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6478,22 +6512,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Samples were obtained from 2028 individuals for HIV sequencing.</t>
+          <t>Sanger sequencing was used.</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6503,22 +6537,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PP280627- PP280757</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Participants received NRTIs, INSTIs, NNRTIs, and protease inhibitors (PIs) before sample sequencing.</t>
+          <t>The GenBank accession numbers for sequenced HIV isolates are PP280627 to PP280757.</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -6528,18 +6562,20 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>237</v>
+      </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>The genes sequenced were protease, reverse transcriptase, and integrase.</t>
+          <t>Samples were obtained from 251 individuals for HIV sequencing.</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6549,22 +6585,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from Malawi.</t>
+          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer were used for sequencing.</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6574,22 +6610,22 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>The samples were obtained between July 2022 and February 2023.</t>
+          <t>All participants were ART-naive, so they had not received any drugs before sample sequencing.</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6599,22 +6635,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>The study used Sanger sequencing for genotypic analysis.</t>
+          <t>All participants were ART-naive, so they had not received any drugs before sample sequencing.</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -6624,22 +6660,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Plasma samples were sequenced.</t>
+          <t>Yes, the paper reports in vitro drug susceptibility data.</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -6649,22 +6685,20 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>64</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure on a treatment regimen.</t>
+          <t>Samples were obtained from a total of 54 individuals in the PURPOSE 1 and PURPOSE 2 trials.</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -6674,22 +6708,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Samples were obtained from 213 individuals with confirmed virologic failure.</t>
+          <t>The paper mentions samples from South Africa and other unspecified countries.</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -6699,22 +6733,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Yes, the paper reports sequences from individuals who had previously received ARV drugs.</t>
+          <t>The specific years from which samples were obtained are not provided in the paper.</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -6724,22 +6758,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (single genome)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Individuals in the study received drugs from the NRTI, NNRTI, PI, and INSTI classes before sample sequencing.</t>
+          <t>No, samples were not cloned prior to sequencing.</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -6749,22 +6783,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>NRTI, CAI</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>The specific drugs received by individuals prior to sequencing are not listed in the provided text.</t>
+          <t>NRTIs and INSTIs were received by individuals in the study.</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -6774,18 +6808,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>TDF, TAF, FTC, LEN</t>
+        </is>
+      </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Protease (PR), reverse transcriptase (RT), and integrase (IN) genes were sequenced.</t>
+          <t>Specific drugs mentioned include emtricitabine, tenofovir, and dolutegravir, lamivudine.</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6795,22 +6833,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>Not available (deposited 2015-2025)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Countries were not specified in the provided content.</t>
+          <t>The sequenced samples were obtained from the years 2015 to 2025.</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -6820,22 +6858,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>The years of sample collection are not specified.</t>
+          <t>The paper does not mention if any sequences were obtained from individuals with virological failure.</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -6845,22 +6883,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Clinical samples were sequenced.</t>
+          <t>The paper does not specify whether the sequences were from individuals who had previously received ARV drugs.</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -6870,4116 +6908,25 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Yes, sequences were obtained from individuals with virological failure.</t>
+          <t>The paper does not provide information on the drug classes received by individuals prior to sequencing.</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Yes, the study was a clinical trial.</t>
-        </is>
-      </c>
-      <c r="E263" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>The paper mentions that data were available for at least 19 individuals.</t>
-        </is>
-      </c>
-      <c r="E264" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI</t>
-        </is>
-      </c>
-      <c r="E265" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Bictegravir, Emtricitabine, Tenofovir Alafenamide, Dolutegravir, Emtricitabine, Tenofovir Disoproxil Fumarate</t>
-        </is>
-      </c>
-      <c r="E266" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports HIV sequences from patient samples.</t>
-        </is>
-      </c>
-      <c r="E267" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>The paper reports the sequencing of drug resistance mutations Including RT, PR, and IN genes.</t>
-        </is>
-      </c>
-      <c r="E268" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>0 (Review paper)</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from Tanzania.</t>
-        </is>
-      </c>
-      <c r="E269" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from studies published until the end of December 2024.</t>
-        </is>
-      </c>
-      <c r="E270" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>2004-2021</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>The paper does not specify the exact method used for sequencing.</t>
-        </is>
-      </c>
-      <c r="E271" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>The paper does not specify the type of clinical samples that were sequenced.</t>
-        </is>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports sequences obtained from individuals with virological failure on a treatment regimen.</t>
-        </is>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>The paper mentions that the meta-analysis included studies with a total of 9685 participants on ART.</t>
-        </is>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
-        </is>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>The paper reports the receipt of NRTIs and NNRTIs by individuals in the study before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>The paper mentions the use of various NRTIs including 3TC, FTC, AZT, and TDF.</t>
-        </is>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are PX133190-PX134237.</t>
-        </is>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>PX133190–PX134237</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>The paper reports the sequencing of the pol gene, which includes the full-length protease (PR) and the first 299 codons of the RT gene.</t>
-        </is>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from China, specifically Nanning City, Guangxi Province.</t>
-        </is>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from 2019 to 2022.</t>
-        </is>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>2019-2022</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>The method used for sequencing was Sanger sequencing, conducted by Sangon Biotech using the Applied Biosystems 3730XL Genetic Analyzer.</t>
-        </is>
-      </c>
-      <c r="E282" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Plasma samples were sequenced in this study. HIV-1 RNA was extracted from plasma samples for sequencing.</t>
-        </is>
-      </c>
-      <c r="E283" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Samples were obtained from 1,260 individuals for HIV sequencing.</t>
-        </is>
-      </c>
-      <c r="E284" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>The study did not have individuals who received antiretroviral drugs before sample sequencing, as it focused on newly diagnosed, ART-naive individuals.</t>
-        </is>
-      </c>
-      <c r="E285" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr"/>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>The study did not have individuals who received antiretroviral drugs before sample sequencing, as it focused on newly diagnosed, ART-naive individuals.</t>
-        </is>
-      </c>
-      <c r="E286" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr"/>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Yes, the sequences were made publicly available and are listed under specific GenBank accession numbers.</t>
-        </is>
-      </c>
-      <c r="E287" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr"/>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>The study reported sequencing of the NC and IN genes.</t>
-        </is>
-      </c>
-      <c r="E288" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>The paper mentions using Sanger sequencing for some methods.</t>
-        </is>
-      </c>
-      <c r="E289" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>The paper does not mention whether samples were cloned prior to sequencing.</t>
-        </is>
-      </c>
-      <c r="E290" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Peripheral blood mononuclear cells (PBMCs) were sequenced.</t>
-        </is>
-      </c>
-      <c r="E291" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>The paper discusses integrase strand transfer inhibitors (INSTIs).</t>
-        </is>
-      </c>
-      <c r="E292" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr"/>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>The drug mentioned in the context of the study is dolutegravir (DTG).</t>
-        </is>
-      </c>
-      <c r="E293" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports HIV sequences from patient samples. Specifically, the HIV-1 gag-protease DNA fragment from a total of 24 patient samples was cloned into pXXLAI, including samples with non-B HIV-1 subtypes and HIV-1 B subtype.</t>
-        </is>
-      </c>
-      <c r="E294" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>The paper reports sequencing of the HIV-1 gag-protease DNA fragment and the capsid and reverse transcriptase sequences from selected viruses to determine the presence of resistance mutations.</t>
-        </is>
-      </c>
-      <c r="E295" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>Yes, the paper mentions that the patient plasma samples were obtained from various clinical studies such as GS-US-380-1490, GS-US-292-0104, GS-US-200-4334, and GS-US-200-4625.</t>
-        </is>
-      </c>
-      <c r="E296" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>The paper states that HIV-1 sequences from a total of 24 patient samples were analyzed and included in the study.</t>
-        </is>
-      </c>
-      <c r="E297" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>The study did not mention the specific drug classes received by individuals before sample sequencing, specifically mentioned that the participants were treatment naive.</t>
-        </is>
-      </c>
-      <c r="E298" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>The study did not mention the specific drugs received by individuals before sample sequencing, specifically mentioned that the participants were treatment naive.</t>
-        </is>
-      </c>
-      <c r="E299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>The paper reports sequencing of the protease, reverse transcriptase, and integrase genes.</t>
-        </is>
-      </c>
-      <c r="E300" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>The paper does not specify the countries from which the sequenced samples were obtained.</t>
-        </is>
-      </c>
-      <c r="E301" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from 1997 to 2019.</t>
-        </is>
-      </c>
-      <c r="E302" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>1997-2019</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>The paper used proviral DNA genotyping of PR/RT/IN using GenoSure Archive (Monogram Biosciences, CA, USA).</t>
-        </is>
-      </c>
-      <c r="E303" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>RT,PR,IN</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>The paper sequenced whole blood samples.</t>
-        </is>
-      </c>
-      <c r="E304" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>PBMC (Whole blood OK)</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Yes, the patients were part of clinical trials.</t>
-        </is>
-      </c>
-      <c r="E305" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>The paper obtained samples from 241 individuals for HIV sequencing.</t>
-        </is>
-      </c>
-      <c r="E306" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>The individuals in the study received NRTIs, INSTIs, and PIs before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E307" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>The individuals in the study received bictegravir, emtricitabine, and tenofovir alafenamide before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E308" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr"/>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>The paper reports sequencing of the whole genome of HIV-1.</t>
-        </is>
-      </c>
-      <c r="E309" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from the United Kingdom.</t>
-        </is>
-      </c>
-      <c r="E310" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained between 2015 and 2021.</t>
-        </is>
-      </c>
-      <c r="E311" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>2015-2021</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>The complete genomic sequencing of HIV was performed using a sequence capture method and assembled into consensus whole genomes using Genomancer.</t>
-        </is>
-      </c>
-      <c r="E312" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>The samples sequenced were from patients with recently acquired HIV-1.</t>
-        </is>
-      </c>
-      <c r="E313" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>A total of 1182 individuals had samples obtained for HIV sequencing.</t>
-        </is>
-      </c>
-      <c r="E314" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>Individuals in the study had not received any ARV drugs before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E315" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>Individuals in the study had not received any ARV drugs before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E316" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr"/>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>Yes, the sequences were made publicly available.</t>
-        </is>
-      </c>
-      <c r="E317" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Yes (Only past sequences)</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>No, the paper does not report HIV sequences from patient samples.</t>
-        </is>
-      </c>
-      <c r="E318" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>249 (uncertain)</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>The paper mentions Italy as the country of the study.</t>
-        </is>
-      </c>
-      <c r="E319" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>The paper does not specify the years from which the sequenced samples were obtained.</t>
-        </is>
-      </c>
-      <c r="E320" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>PR, RT, IN (presumably)</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>The paper does not specify the type of samples that were sequenced.</t>
-        </is>
-      </c>
-      <c r="E321" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Yes, the paper discusses virological failure in individuals on treatment regimens.</t>
-        </is>
-      </c>
-      <c r="E322" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>The paper does not specify the number of individuals from whom samples were obtained for sequencing.</t>
-        </is>
-      </c>
-      <c r="E323" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>Yes, the paper includes individuals who had previously received ARV drugs.</t>
-        </is>
-      </c>
-      <c r="E324" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>The paper mentions integrase inhibitors and protease inhibitors.</t>
-        </is>
-      </c>
-      <c r="E325" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>The paper specifically mentions dolutegravir and darunavir.</t>
-        </is>
-      </c>
-      <c r="E326" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>The integrase region was sequenced, and mutations in the reverse transcriptase and protease regions were also analyzed when available.</t>
-        </is>
-      </c>
-      <c r="E327" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from Mozambique.</t>
-        </is>
-      </c>
-      <c r="E328" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Mozambique</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained between 2023 and 2024.</t>
-        </is>
-      </c>
-      <c r="E329" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>2022-2024</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>The Sanger method was used for sequencing.</t>
-        </is>
-      </c>
-      <c r="E330" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>RT,IN</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Plasma samples were sequenced.</t>
-        </is>
-      </c>
-      <c r="E331" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Yes, sequences were obtained from individuals with virological failure on a treatment regimen.</t>
-        </is>
-      </c>
-      <c r="E332" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>28 individuals had samples obtained for HIV sequencing.</t>
-        </is>
-      </c>
-      <c r="E333" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
-        </is>
-      </c>
-      <c r="E334" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Individuals received NRTIs, NNRTIs, and protease inhibitors.</t>
-        </is>
-      </c>
-      <c r="E335" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>NRTI,NNRTI,INSTI</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>Specific drugs were not detailed, but DTG-based regimens were used.</t>
-        </is>
-      </c>
-      <c r="E336" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Yes (some)</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are: PQ893197, PQ893192, OQ985810, OR259747, and PQ893191.</t>
-        </is>
-      </c>
-      <c r="E337" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>PQ893197, PQ893192, OQ985810, OR259747 and PQ893191 &amp; submission ID: 2961867)</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>The HIV genes reported to have been sequenced are the protease (PR) and reverse transcriptase (RT) genes.</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from Cameroon.</t>
-        </is>
-      </c>
-      <c r="E339" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from January 2022 to April 2023.</t>
-        </is>
-      </c>
-      <c r="E340" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>2022-2023</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>The method used for sequencing was Sanger sequencing.</t>
-        </is>
-      </c>
-      <c r="E341" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>The sequenced samples were plasma samples with viral load ≥ 1000 copies/ml.</t>
-        </is>
-      </c>
-      <c r="E342" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Yes, the study obtained sequences from individuals with virological failure on a treatment regimen.</t>
-        </is>
-      </c>
-      <c r="E343" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>Samples were obtained from 203 individuals for HIV sequencing.</t>
-        </is>
-      </c>
-      <c r="E344" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
-        </is>
-      </c>
-      <c r="E345" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>Individuals in the study received NRTI, NNRTI, and PI/r drug classes before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E346" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>41029850</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Individuals in the study received AZT, 3TC, ABC, LPV/r, ATV/r, TDF, DTG, and EFV prior to sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E347" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="E348" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="E349" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>Yes.</t>
-        </is>
-      </c>
-      <c r="E350" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="E351" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="E352" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>NRTIs, Integrase inhibitors.</t>
-        </is>
-      </c>
-      <c r="E353" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI, CAI</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>Emtricitabine, tenofovir alafenamide, lenacapavir, bictegravir.</t>
-        </is>
-      </c>
-      <c r="E354" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>No, the study does not report new HIV sequences from patient samples.</t>
-        </is>
-      </c>
-      <c r="E355" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>The paper reports sequencing of the protease, RT, and integrase genes.</t>
-        </is>
-      </c>
-      <c r="E356" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from Uganda.</t>
-        </is>
-      </c>
-      <c r="E357" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>The samples were obtained from 2018 to 2023.</t>
-        </is>
-      </c>
-      <c r="E358" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>2018-2023</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>The paper does not specify the exact method used for sequencing.</t>
-        </is>
-      </c>
-      <c r="E359" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>RT,PR,IN</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>The paper does not specify the type of samples sequenced, such as plasma or PBMCs.</t>
-        </is>
-      </c>
-      <c r="E360" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>Sanger (not stated)</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports sequences obtained from individuals with virological failure.</t>
-        </is>
-      </c>
-      <c r="E361" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>Samples were obtained from 235 individuals living with HIV.</t>
-        </is>
-      </c>
-      <c r="E362" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports sequences from individuals who had previously received ARV drugs.</t>
-        </is>
-      </c>
-      <c r="E363" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>Participants received NRTI, NNRTI, PI, or INSTI drug classes before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E364" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>NRTI,NNRTI,PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>Specific drugs received included ABC, AZT, D4T, TDF, DTG, DRV, ETR, LPV, and RAL.</t>
-        </is>
-      </c>
-      <c r="E365" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>The GenBank accession number for sequenced HIV isolates is PV187006.</t>
-        </is>
-      </c>
-      <c r="E366" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>PV187006</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>The near full-length genome (NFLG) of HIV-1 was sequenced, covering multiple genes.</t>
-        </is>
-      </c>
-      <c r="E367" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from China.</t>
-        </is>
-      </c>
-      <c r="E368" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained in 2023 and 2025.</t>
-        </is>
-      </c>
-      <c r="E369" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>The sequencing method used was Sanger sequencing.</t>
-        </is>
-      </c>
-      <c r="E370" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>No, the samples were not cloned prior to sequencing.</t>
-        </is>
-      </c>
-      <c r="E371" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>Plasma and whole-blood samples were sequenced.</t>
-        </is>
-      </c>
-      <c r="E372" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>One individual had samples obtained for HIV sequencing.</t>
-        </is>
-      </c>
-      <c r="E373" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>The individuals in the study had not received any drug classes before sample sequencing as they were ART-naive.</t>
-        </is>
-      </c>
-      <c r="E374" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>The individuals in the study had not received any drugs before sample sequencing as they were ART-naive.</t>
-        </is>
-      </c>
-      <c r="E375" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>Yes, the sequences from the paper were made publicly available.</t>
-        </is>
-      </c>
-      <c r="E376" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>HIV-1 protease was reported to have been sequenced.</t>
-        </is>
-      </c>
-      <c r="E377" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>Yes (site-directed mutants)</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>The paper does not mention whether samples were cloned prior to sequencing.</t>
-        </is>
-      </c>
-      <c r="E378" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>The paper does not specify the type of samples that were sequenced.</t>
-        </is>
-      </c>
-      <c r="E379" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>The paper discusses the use of protease inhibitors, indicating the drug class received.</t>
-        </is>
-      </c>
-      <c r="E380" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>The paper specifically mentions darunavir as a drug used in the study.</t>
-        </is>
-      </c>
-      <c r="E381" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>Yes (recombinant clones)</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are PQ735970-PQ735985.</t>
-        </is>
-      </c>
-      <c r="E382" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>PQ735970–PQ735985</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>The Pol region was reported to have been sequenced.</t>
-        </is>
-      </c>
-      <c r="E383" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from China and the United States.</t>
-        </is>
-      </c>
-      <c r="E384" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from 1978 to 2023.</t>
-        </is>
-      </c>
-      <c r="E385" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>The study used Sanger sequencing.</t>
-        </is>
-      </c>
-      <c r="E386" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>No HIV-1 samples from patients were sequenced in this study. The study was based on laboratory-reconstructed viruses, which differ from sequencing patient samples.</t>
-        </is>
-      </c>
-      <c r="E387" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>Yes, the sequences were made publicly available.</t>
-        </is>
-      </c>
-      <c r="E388" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are PP280627 to PP280757.</t>
-        </is>
-      </c>
-      <c r="E389" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>PP280627- PP280757</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>The partial reverse transcriptase (RT) gene was sequenced.</t>
-        </is>
-      </c>
-      <c r="E390" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from Senegal.</t>
-        </is>
-      </c>
-      <c r="E391" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained between 2017 and 2018.</t>
-        </is>
-      </c>
-      <c r="E392" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>2017-2018</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>Sequencing was performed using the Big Dye Terminator v3.1 method and ABI 3100 Avant sequencer.</t>
-        </is>
-      </c>
-      <c r="E393" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>Both dried blood spots (DBS) and plasma samples were sequenced.</t>
-        </is>
-      </c>
-      <c r="E394" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>Samples were obtained from 331 antiretroviral therapy-naive patients.</t>
-        </is>
-      </c>
-      <c r="E395" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>The individuals were antiretroviral therapy-naive, so no drug classes were received before sampling.</t>
-        </is>
-      </c>
-      <c r="E396" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>The individuals were antiretroviral therapy-naive, so no specific drugs were received before sampling.</t>
-        </is>
-      </c>
-      <c r="E397" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>Yes, the sequences were deposited in the National Institutes of Health GenBank database.</t>
-        </is>
-      </c>
-      <c r="E398" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports in vitro drug susceptibility data based on Sanger sequencing results.</t>
-        </is>
-      </c>
-      <c r="E399" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr"/>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>The paper mentions sequencing for drug resistance mutations primarily in the reverse transcriptase, protease, and integrase genes.</t>
-        </is>
-      </c>
-      <c r="E400" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from Uganda.</t>
-        </is>
-      </c>
-      <c r="E401" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained between January and November 2021.</t>
-        </is>
-      </c>
-      <c r="E402" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>The paper used Sanger sequencing technology for sequencing.</t>
-        </is>
-      </c>
-      <c r="E403" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>RT, PR, IN</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>Plasma samples were sequenced.</t>
-        </is>
-      </c>
-      <c r="E404" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports sequences obtained from individuals with virological failure on their treatment regimen.</t>
-        </is>
-      </c>
-      <c r="E405" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>Samples were obtained from 333 individuals for HIV sequencing.</t>
-        </is>
-      </c>
-      <c r="E406" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>Yes, the paper reports HIV sequences from individuals who had previously received ARV drugs.</t>
-        </is>
-      </c>
-      <c r="E407" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>Individuals received drugs from the NRTI, NNRTI, PI, and INSTI classes before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E408" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>Drugs received included Dolutegravir, Abacavir, Zidovudine, Tenofovir, Lopinavir, Lamivudine, Darunavir, Efavirenz, and Nevirapine.</t>
-        </is>
-      </c>
-      <c r="E409" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are not provided in the paper.</t>
-        </is>
-      </c>
-      <c r="E410" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>The HIV genes sequenced include capsid, protease, reverse transcriptase, and integrase.</t>
-        </is>
-      </c>
-      <c r="E411" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from multiple countries, including South Africa.</t>
-        </is>
-      </c>
-      <c r="E412" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>The specific years from which the sequenced samples were obtained are not provided in the paper.</t>
-        </is>
-      </c>
-      <c r="E413" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>Not provided</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>Next-generation sequencing (NGS) was used for sequencing.</t>
-        </is>
-      </c>
-      <c r="E414" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>Yes (single genome)</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>No, samples were not cloned prior to sequencing.</t>
-        </is>
-      </c>
-      <c r="E415" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>RT,PR,IN,CA</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>Plasma samples were sequenced.</t>
-        </is>
-      </c>
-      <c r="E416" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>NGS</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>Yes, sequences were obtained from individuals with virological failure.</t>
-        </is>
-      </c>
-      <c r="E417" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>Yes, the patients were part of clinical trials.</t>
-        </is>
-      </c>
-      <c r="E418" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>Yes (PrEP)</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>A total of 53 individuals had samples obtained for HIV sequencing in the resistance analysis population (RAP).</t>
-        </is>
-      </c>
-      <c r="E419" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>Participants received NRTIs and INSTIs before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E420" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>NRTI, CAI</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>Drugs received include tenofovir disoproxil fumarate (TDF), lamivudine (3TC), and dolutegravir (DTG).</t>
-        </is>
-      </c>
-      <c r="E421" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>The paper reports sequencing of the pol gene, including PR, RT, and IN regions.</t>
-        </is>
-      </c>
-      <c r="E422" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>0 (Review paper)</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained from Kenya, Uganda, Tanzania, and Ethiopia.</t>
-        </is>
-      </c>
-      <c r="E423" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>The sequenced samples were obtained between 2015 and 2025.</t>
-        </is>
-      </c>
-      <c r="E424" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>Not available (deposited 2015-2025)</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>The specific method used for sequencing is not mentioned in the paper.</t>
-        </is>
-      </c>
-      <c r="E425" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>PR, RT, IN</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>The paper does not specify the type of clinical specimens sequenced.</t>
-        </is>
-      </c>
-      <c r="E426" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>The paper does not specify the number of individuals from whom samples were obtained for sequencing.</t>
-        </is>
-      </c>
-      <c r="E427" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>The paper does not specify the drug classes received by individuals before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E428" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>The paper does not specify the drugs received by individuals before sample sequencing.</t>
-        </is>
-      </c>
-      <c r="E429" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E262"/>
+  <dimension ref="A1:E358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,34 +446,34 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>GPT-4o FT Answer</t>
+          <t>GPT-4o FT-200 Answer</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>GPT-4o FT Correct</t>
+          <t>GPT-4o FT-200 Correct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19104010</t>
+          <t>18715920</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ABI Prism BigDye Terminator sequencing</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -508,7 +508,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21115794</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -521,11 +521,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>0</v>
       </c>
@@ -533,22 +529,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23749954</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -558,22 +554,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23749954</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>HQ873097-HQ873169</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -583,22 +579,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24227862</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -608,22 +604,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25637519</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -633,22 +629,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26246578</t>
+          <t>24227862</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -658,7 +654,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26559830</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -668,12 +664,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -683,12 +679,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27009474</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -698,7 +694,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -708,22 +704,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27009474</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -733,20 +729,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -756,22 +754,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -781,22 +779,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>26559830</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -806,12 +804,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -821,7 +819,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -831,20 +829,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2015</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -854,22 +854,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30803972</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -879,22 +879,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>31988104</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -904,20 +904,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31988104</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>14</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -927,22 +929,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>32601157</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Virus isolates</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -952,17 +954,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -977,18 +979,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>EFV, DTG, TDF, 3TC</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1002,20 +1002,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>51</v>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No evidence</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1025,22 +1027,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1050,22 +1052,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>plasma RNA</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1075,17 +1077,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1100,22 +1102,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>51</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1125,22 +1125,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>gag-pol</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1150,20 +1150,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>6</v>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1173,22 +1175,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1198,22 +1200,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1223,17 +1225,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1248,22 +1250,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1273,22 +1275,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>36571282</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1298,22 +1300,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1323,22 +1325,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>120 * 76% = 95, or 120 or 129</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>viral isolates</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1348,22 +1350,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1373,24 +1375,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RT, IN</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
         <v>0</v>
       </c>
@@ -1398,24 +1396,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI</t>
-        </is>
-      </c>
+          <t>EFV, DTG, TDF, 3TC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
         <v>0</v>
       </c>
@@ -1423,24 +1417,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>51</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>0</v>
       </c>
@@ -1448,22 +1436,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>14</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
         <v>0</v>
       </c>
@@ -1471,24 +1457,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>2021-2022</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
         <v>0</v>
       </c>
@@ -1496,24 +1478,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2019-2020</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
         <v>0</v>
       </c>
@@ -1521,17 +1499,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1546,12 +1524,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1571,12 +1549,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1596,22 +1574,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NRTI, INSTI</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1621,22 +1597,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1646,22 +1622,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1671,22 +1647,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1696,22 +1672,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>36694270</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI, INSTI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1721,22 +1697,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>36694270</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1746,22 +1722,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>62 or 3</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1771,22 +1747,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1796,22 +1772,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>36779485</t>
+          <t>36415058</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1821,22 +1797,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36851704</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1846,22 +1822,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>36851704</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TDF, FTC, 3TC, DTG, ATV/r, LPV/r</t>
+          <t>Clinical samples</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1871,22 +1847,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>36961945</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1896,17 +1870,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>36967989</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1921,22 +1895,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>36982978</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>120 * 76% = 95, or 120 or 129</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1946,22 +1920,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>36982978</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1971,22 +1945,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>36982978</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -1996,7 +1970,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>36982978</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2006,12 +1980,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2021,22 +1995,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>36982978</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NRTI, PI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2046,24 +2020,18 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>36982978</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Lamivudine (3TC), Abacavir (ABC), Zidovudine (AZT), Stavudine (D4T), Emtricitabine (FTC), Didanosine (DDI), Tenofovir (TFV), Tenofovir alafenamide (TAF), Darunavir, Saquinavir, Lopinavir</t>
-        </is>
-      </c>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>14</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
         <v>0</v>
       </c>
@@ -2071,24 +2039,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>37039023</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NFLG, PR, RT, IN, Env</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Near full length genome</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
         <v>0</v>
       </c>
@@ -2096,24 +2060,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>37071019</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
         <v>0</v>
       </c>
@@ -2121,24 +2081,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>37104815</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Whole Blood, Semen</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Plasma; PBMC</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
         <v>0</v>
       </c>
@@ -2146,12 +2102,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>37147875</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2171,7 +2127,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2181,12 +2137,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2196,24 +2152,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>37279764</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
         <v>0</v>
       </c>
@@ -2221,24 +2173,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>BIC, FTC, TAF</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
         <v>0</v>
       </c>
@@ -2246,20 +2194,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1651</v>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2269,22 +2219,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2294,22 +2244,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2319,22 +2269,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2344,22 +2294,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2369,7 +2319,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2379,12 +2329,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tenofovir, lamivudine, efavirenz, nevirapine, lopinavir, ritonavir</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2394,22 +2344,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No, the paper does not report HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2419,22 +2369,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2444,22 +2394,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>37515095</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>The paper does not specify which HIV genes were sequenced.</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2469,22 +2419,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing, Oxford nanopore</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Oxford Nanopore sequencing</t>
+          <t>The paper does not specify the type of samples that were sequenced.</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2494,22 +2444,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>527</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>594</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2519,22 +2467,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Data as of August 2021</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2544,22 +2492,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2569,22 +2517,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2594,22 +2542,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2619,22 +2567,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2644,22 +2592,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Lopinavir (LPV), Dolutegravir (DTG), Raltegravir (RAL)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2669,22 +2617,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2694,20 +2642,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2717,22 +2667,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2742,12 +2692,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2757,7 +2707,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>TDF, FTC, 3TC, ABC, ZDV, EVF, NVP, ATV/r, LPV/r, RAL, DTG, DRV/r, ETR, RPV, BIC, CAB</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2767,7 +2717,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>36851760</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2782,7 +2732,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Etravirine (ETR), Dolutegravir (DTG), Darunavir (DRV), Ritonavir (RTV), Tenofovir (TFV), Lamivudine (3TC), Emtricitabine (FTC), Abacavir (ABC), Efavirenz (EFV)</t>
+          <t>Unspecified NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2792,22 +2742,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>37574435</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>70 or 79</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2817,22 +2767,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>37574435</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2842,22 +2790,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>37585352</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Near full length genome</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2867,22 +2815,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>37585352</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2892,7 +2840,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>37593123</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2902,12 +2850,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Viral RNA from cultured virus</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2917,20 +2865,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>37626789</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>551</v>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2940,22 +2890,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>37674678</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2965,22 +2915,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma, CSF, PBMC</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -2990,22 +2940,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3015,22 +2965,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3040,22 +2990,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3065,22 +3015,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3090,22 +3040,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37017009</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Next-generation sequencing (Illumina MiSeq).</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3115,22 +3065,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3140,12 +3090,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37039023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3155,7 +3105,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), Lamivudine (3TC), Dolutegravir (DTG)</t>
+          <t>NC_001802</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3165,24 +3115,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>37775947</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>South America, Africa, USA, Asia, Australia, Europe</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
         <v>0</v>
       </c>
@@ -3190,22 +3136,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>37775947</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3215,22 +3161,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NFLG, gp120</t>
+          <t>Whole Blood, Semen</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Near full length genome</t>
+          <t>Plasma RNA and HIV DNA</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3240,22 +3186,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37112971</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>K03455 for PR-RT and INT regions</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3265,17 +3211,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3290,7 +3236,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3305,7 +3251,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3315,7 +3261,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3330,7 +3276,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Emtricitabine (FTC), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Darunavir (DRV), Lopinavir (LPV), Atazanavir (ATV)</t>
+          <t>Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir disoproxil fumarate (TDF)</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3340,7 +3286,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3350,12 +3296,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Illumina sequencing</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3365,12 +3311,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3390,22 +3336,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3415,22 +3361,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -3440,7 +3386,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3455,7 +3401,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NVP, ETR, ABC, 3TC, DTG, ATV, LPV, RAL, SQV</t>
+          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3465,22 +3411,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3490,22 +3436,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3515,22 +3461,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1651</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3540,17 +3484,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3565,20 +3509,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>37993493</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>33</v>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3588,22 +3534,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3613,22 +3559,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3638,12 +3584,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3653,7 +3599,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3663,22 +3609,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020, 2022, 2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3688,22 +3634,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3713,12 +3659,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3728,7 +3674,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3738,22 +3684,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37381002</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -3763,20 +3709,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>5</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -3786,22 +3734,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3811,22 +3759,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2019-2022</t>
+          <t>EFV, NVP, RPV, ETR, DOR</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3836,22 +3784,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37495103</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ABI PRISM sequencing</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3861,22 +3809,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3886,20 +3834,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>0</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3909,22 +3859,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Canada, Tanzania, Brazil, Nigeria</t>
+          <t>Gag, Pol, Env, Integnase RT</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3934,22 +3884,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2012-2014, 2019, 2021, 2018</t>
+          <t>Next-Generation Sequencing (NGS)</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3959,22 +3909,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -3984,22 +3934,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37515095</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -4009,22 +3959,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>379</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>391</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -4034,22 +3982,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>ABI 3500</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -4059,7 +4007,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4074,7 +4022,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -4084,22 +4032,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>38140667</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), Lamivudine (3TC), Dolutegravir (DTG), Rilpivirine (RPV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -4109,22 +4057,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>2016-2017, 2019-2020</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -4134,22 +4082,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -4159,7 +4107,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4169,12 +4117,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4184,7 +4132,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4194,12 +4142,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Lamivudine (3TC)</t>
+          <t>EFV, ATV, FTC, TDF</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -4209,20 +4157,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>227</v>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Samples were obtained from 488 individuals for HIV sequencing.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4232,20 +4182,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>47</v>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Samples were obtained from 54 participants who were diagnosed with HIV during the trial.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4255,22 +4207,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from England, as the trial was conducted across Sexual Health Services in England.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4280,12 +4232,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4295,7 +4247,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Yes, the patients were part of the PrEP Impact trial.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4305,22 +4257,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TDF, FTC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Specific drugs received included TDF, FTC, DTG, DRV, 3TC, ABC, and RAL, reflecting the treatments received prior to HIV sequencing.</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4330,22 +4282,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2006-2024</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from 2022-2024.</t>
+          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4355,22 +4307,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Next generation sequencing was used for genotypic resistance tests.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4380,22 +4332,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Plasma RNA and proviral DNA from PBMCs were sequenced.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4405,22 +4357,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Yes, the patient was enrolled in the Swiss HIV Cohort Study and participated in the TMC-125 trial.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4430,22 +4382,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), ritonavir (RTV), didanosine (ddI), abacavir (ABC), tenofovir disoproxil (TDF), lopinavir (LPV), etravirine (ETR), atazanavir (ATV), raltegravir (RAL), emtricitabine (FTC), dolutegravir (DTG), darunavir (DRV), and bictegravir (BIC).</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4455,20 +4407,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>1677</v>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>PI, INSTI</t>
+        </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Samples from 1667 individuals were included in the mutation analysis.</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4478,22 +4432,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sanger  </t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>The paper used a PCR-based method for sequencing the HIV-1 pol gene fragments.</t>
+          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4503,22 +4457,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>37546367</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>The paper mentions that plasma HIV-1 RNA samples were sequenced.</t>
+          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4528,22 +4482,20 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>AZT, 3TC, TDF, ABC, EFV, NVP, LPV, RTV, ATV (RTV is for boosting)</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>The paper mentioned specific drugs such as atazanavir/ritonavir and lopinavir/ritonavir received prior to sequencing. The NRTIs lamivudine, zidovudine, and tenofovir were received before sequencing</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4553,24 +4505,20 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>The GenBank accession numbers for the sequenced HIV isolates are not provided in the text.</t>
-        </is>
-      </c>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="n">
         <v>0</v>
       </c>
@@ -4578,22 +4526,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>The type of samples sequenced were plasma or serum from patients.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4603,22 +4551,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>The study included individuals who were ART-naïve at the time of sample sequencing, so they had not received any drug classes before sequencing.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4628,12 +4576,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4643,7 +4591,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>The study included individuals who were ART-naïve at the time of sample sequencing, so they had not received any drugs before sequencing.</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4653,22 +4601,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>The sequencing method used was the ViroSeq Genotyping System.</t>
+          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4678,22 +4626,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>37573167</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>The sequenced samples were clinical specimens from mother-child pairs with confirmed vertical transmission of HIV-1.</t>
+          <t>Specific drugs not reported</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4703,22 +4651,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>37574435</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Individuals in the study received zidovudine (ZDV), lamivudine (3TC), nevirapine (NVP), lopinavir/ritonavir, and efavirenz (EFV) before sample sequencing.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4728,22 +4676,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>HIV drug resistance (HIVDR) was retrospectively characterized among 20 children and adolescents with HIV with virologic failure on non-nucleoside reverse transcriptase inhibitor (NNRTI)-based therapy, and virologic response in those switched to dolutegravir (DTG)-based therapy described.</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -4753,22 +4701,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AZT, ABC, 3TC, TDF, ATV, LPV, RTV, DTG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>The study involved participants on various ART regimens including TDF/3TC/DTG, AZT/3TC/DTG, ABC/3TC/DTG, ABC/3TC/LPVr, TDF/3TC/ATVr, AZT/3TC/ATVr, and others before sample sequencing.</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4778,20 +4726,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>20</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Samples were obtained from 2028 individuals for HIV sequencing.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4801,22 +4751,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>The study used population sequencing level.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4826,22 +4776,20 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>PBMC</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>551</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>The paper mentions that whole blood samples were used for sequencing.</t>
+          <t>554</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4851,22 +4799,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+          <t>2007-2019</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Participants received Tenofovir, INSTIs, NNRTIs, and PIs before sample sequencing.</t>
+          <t>2017 to 2019</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4876,20 +4824,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>40839365</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>212</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Samples were obtained from 213 individuals with confirmed virologic failure.</t>
+          <t>ABI-3730 DNA genetic analyzer</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -4899,22 +4849,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>The paper mentions resistance testing data for 22 participants.</t>
+          <t>NRTI, INSTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4924,22 +4874,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>The paper does not detail the specific method used for sequencing.</t>
+          <t>Not specified in the provided text</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4949,22 +4899,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples that were sequenced.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -4974,22 +4924,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Yes the paper reports HIV sequences from patient samples.</t>
+          <t>ABI 3730XL</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -4999,20 +4949,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>0</v>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>A total of 9685 individuals had samples obtained for HIV sequencing.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -5022,22 +4974,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from studies published up to 2024, covering various years including 2005-2021.</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5047,22 +4999,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the RT and integrase gene.</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5072,22 +5024,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>The paper does not specify the exact sequencing method used.</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5097,7 +5049,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5107,12 +5059,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of clinical samples sequenced.</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5122,22 +5074,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>The drugs received by individuals in the study include TDF, 3TC, DTG, FTC, AZT, and LPV/r.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5147,20 +5099,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>1048</v>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Samples were obtained from 1,260 individuals.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5170,22 +5124,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>There were no GenBank accession numbers.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5195,20 +5149,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>0</v>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>NRTIs, INSTIs</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -5218,22 +5174,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5243,24 +5199,20 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
+          <t>4559 and 3097</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="n">
         <v>0</v>
       </c>
@@ -5268,22 +5220,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>NFLG, gp120</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>env</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5293,7 +5245,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5303,12 +5255,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>plasma viral RNA</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5318,22 +5270,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>37872202</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>gp120</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>None reported</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5343,22 +5295,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5368,22 +5320,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Yes, the paper reports HIV-1 sequences from patient plasma samples.</t>
+          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5393,20 +5345,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>37880705</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>0</v>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The paper involved 24 patient samples for HIV sequencing.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5416,22 +5370,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>The paper mentions the use of population sequencing.</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5441,22 +5395,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The paper sequenced viral supernatants obtained from patient isolates.</t>
+          <t>d4T, 3TC, AZT, NVP</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5466,22 +5420,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>37896860</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Yes, the paper mentions that the patient plasma samples were obtained from clinical studies.</t>
+          <t>RT, PI</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5491,22 +5445,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>GenBank accession numbers not provided.</t>
+          <t>MiSeq sequencing platform</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5516,20 +5470,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
-        <v>223</v>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>241 individuals had samples obtained for HIV sequencing.</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5539,22 +5495,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The specific countries are not mentioned in the paper.</t>
+          <t>TDF, FTC, EFV</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5564,22 +5520,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>The GenoSure Archive method was used for sequencing.</t>
+          <t>Viral RNA</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5589,22 +5545,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>No, the study included individuals without prior virological failure.</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5614,22 +5570,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from the United Kingdom.</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5639,22 +5595,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Whole genome</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The paper reports sequencing of the entire HIV genome, including nonintegrase genes.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5664,22 +5620,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>The paper used a sequence capture method and the short read data were assembled into consensus whole genomes using Canu Genomancer.</t>
+          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5689,22 +5645,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Yes, the paper mentions sequences obtained from individuals with virological failure.</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5714,22 +5670,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Full genome, NFLG</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Yes, the paper reports sequences from individuals who had previously received ARV drugs.</t>
+          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5739,7 +5695,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5754,7 +5710,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>The individuals in the study received integrase strand transfer inhibitors (INSTIs) before sample sequencing.</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5764,7 +5720,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5779,7 +5735,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>The individuals in the study received raltegravir, dolutegravir, elvitegravir, or bictegravir before sample sequencing.</t>
+          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5789,22 +5745,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>No, the study does not report HIV sequences from patient samples.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -5814,22 +5770,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>249 (uncertain)</t>
+          <t>TDF, FTC</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>The paper does not specify the number of individuals from whom samples were obtained for sequencing.</t>
+          <t>TDF/TAF with FTC</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5839,22 +5795,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>The paper does not mention any countries from which sequenced samples were obtained.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5864,22 +5820,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>The paper does not report sequencing of specific HIV genes.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5889,22 +5845,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>The paper does not detail any sequencing methods.</t>
+          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5914,7 +5870,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5924,12 +5880,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples sequenced.</t>
+          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5939,22 +5895,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>The paper does not mention any sequences obtained from individuals with virological failure.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5964,22 +5920,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>The paper does not report HIV sequences from individuals who had previously received ARV drugs.</t>
+          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -5989,7 +5945,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5999,12 +5955,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>The paper does not specify drug classes received by individuals prior to sequencing.</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -6014,7 +5970,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6024,12 +5980,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DTG, DRV/r</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>The paper does not provide specific drug names received by individuals before sequencing.</t>
+          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6039,22 +5995,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates were not provided in the paper.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6064,22 +6020,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>The samples were obtained from 2023 to 2024.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6089,22 +6045,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DTG (no other ARVs specified)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Specific drugs like Tenofovir, Lamivudine, Emtricitabine, Efavirenz were received by individuals in the study before sample sequencing.</t>
+          <t>HIV from plasma</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6114,22 +6070,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>41029850</t>
+          <t>38072961</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">PQ893197, PQ893192, OQ985810, OR259747 and PQ893191 &amp; submission ID: 2961867) </t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>PQ893197, PQ893192, OQ985810, OQ259747, and PQ893191.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6139,20 +6095,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C231" t="n">
-        <v>10</v>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>182 participants received at least one dose of study drug, and those who met virologic failure criteria were included in the resistance analysis population.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6162,22 +6120,20 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>5</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from the USA and the Dominican Republic.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6187,22 +6143,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>The samples were obtained between 22 November 2019 and 27 August 2020.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6212,22 +6168,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>The paper does not specify the exact sequencing method used.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -6237,7 +6193,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6247,12 +6203,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>The paper discusses mutations in several HIV genes, including those conferring resistance.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -6262,22 +6218,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Specific drugs received included AZT, TDF, D4T, and TDF.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -6287,12 +6243,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6302,7 +6258,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>No, samples were not cloned prior to sequencing.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6312,22 +6268,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Whole genome</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>The sequenced genes include the near full-length genome (NFLG), specifically mentioning regions of vif and env genes, and the pol gene.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6337,7 +6293,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6347,12 +6303,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>The individuals in the study had not received any drugs before sample sequencing.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -6362,7 +6318,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6372,12 +6328,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>BIC, FTC, TAF, EVG</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>The individuals in the study had not received any drugs before sample sequencing.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -6387,22 +6343,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>The paper does not mention whether samples were cloned prior to sequencing.</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -6412,22 +6368,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>The paper does not report specific HIV genes that were sequenced.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6437,22 +6393,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>The paper does not describe the sequencing method used.</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6462,7 +6418,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6472,12 +6428,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>The samples were obtained from China and the United States.</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6487,22 +6443,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>The samples were obtained from 1978 to 2023.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6512,22 +6468,20 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>37</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Sanger sequencing was used.</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6537,22 +6491,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PP280627- PP280757</t>
+          <t>2008-2019</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>The GenBank accession numbers for sequenced HIV isolates are PP280627 to PP280757.</t>
+          <t>2018-2019</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -6562,20 +6516,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>237</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Samples were obtained from 251 individuals for HIV sequencing.</t>
+          <t>High-throughput sequencing</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6585,22 +6541,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer were used for sequencing.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6610,7 +6566,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6625,7 +6581,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>All participants were ART-naive, so they had not received any drugs before sample sequencing.</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6635,7 +6591,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6650,7 +6606,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>All participants were ART-naive, so they had not received any drugs before sample sequencing.</t>
+          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -6660,22 +6616,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Yes, the paper reports in vitro drug susceptibility data.</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -6685,20 +6641,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
-        <v>64</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Samples were obtained from a total of 54 individuals in the PURPOSE 1 and PURPOSE 2 trials.</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -6708,22 +6666,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>The paper mentions samples from South Africa and other unspecified countries.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -6733,22 +6691,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>The specific years from which samples were obtained are not provided in the paper.</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -6758,22 +6716,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>No, samples were not cloned prior to sequencing.</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -6783,22 +6741,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>NRTI, CAI</t>
+          <t>RT, CA</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NRTIs and INSTIs were received by individuals in the study.</t>
+          <t>Gag, Pol</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -6808,22 +6766,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>TDF, TAF, FTC, LEN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Specific drugs mentioned include emtricitabine, tenofovir, and dolutegravir, lamivudine.</t>
+          <t>Plasma viral RNA</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6833,22 +6791,20 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>40391923</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Not available (deposited 2015-2025)</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>227</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>The sequenced samples were obtained from the years 2015 to 2025.</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -6858,22 +6814,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>The paper does not mention if any sequences were obtained from individuals with virological failure.</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -6883,22 +6839,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT,IN</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>The paper does not specify whether the sequences were from individuals who had previously received ARV drugs.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -6908,25 +6864,2405 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Stanford algorithm</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2006-2024</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>From 1996 to 2024.</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>1677</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>1667</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>40490983</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Plasma RNA.</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ViroSeq Genotyping System</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Patient samples</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV), Abacavir (ABC), Didanosine (DDI)</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>HIV-1 pol</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Sanger, NGS</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>AZT, ABC, 3TC, TDF, ATV, LPV, RTV, DTG</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, DTG, ABC, ZDV, AZT, LPVr, ATVr</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>20</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Whole blood</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Tenofovir, Emtricitabine, Instis, NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>7 (Uncertain)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2004-2021</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>1,260 newly diagnosed, ART-naive individuals.</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes  </t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>RT, IN, NC, Env</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NC, IN</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Sanger, NGS</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Plasma samples</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Population sequencing</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>PBMC (Whole blood OK)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Whole blood</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Whole genome sequencing</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Clinical specimens</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Yes (Only past sequences)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>249 (uncertain)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>PR, RT, IN (presumably)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Plasma (presumably)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>PI, INSTI, NRTI (presumably)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>DTG, DRV/r</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2022-2024</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>DTG (no other ARVs specified)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>USA, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>235</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2018-2023</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>AZT, D4T, TDF, ABC, DTG</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Near full-length genome (NFLG), partial pol gene, vif, env</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Yes (site-directed mutants)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>China, United States</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>1978 to 2023</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>PP280627- PP280757</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>PP280627 to PP280757</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>64</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2021 to 2023</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>NRTI, CAI</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs.</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
           <t>41140464</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Not available (deposited 2015-2025)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2015-2025</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
         <is>
           <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C358" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>The paper does not provide information on the drug classes received by individuals prior to sequencing.</t>
-        </is>
-      </c>
-      <c r="E262" t="n">
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E358"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,7 +521,11 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
@@ -1388,7 +1392,11 @@
           <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
@@ -1409,7 +1417,11 @@
           <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
@@ -1428,7 +1440,11 @@
       <c r="C41" t="n">
         <v>51</v>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
@@ -1449,7 +1465,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
@@ -1470,7 +1490,11 @@
           <t>2021-2022</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
@@ -1491,7 +1515,11 @@
           <t>RT, IN</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
@@ -2031,7 +2059,11 @@
       <c r="C66" t="n">
         <v>14</v>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
@@ -2052,7 +2084,11 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
@@ -2073,7 +2109,11 @@
           <t>2019-2020</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
@@ -2094,7 +2134,11 @@
           <t>RT, IN</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
@@ -2165,7 +2209,11 @@
           <t>NRTI, INSTI</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
@@ -2186,7 +2234,11 @@
           <t>BIC, FTC, TAF</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
@@ -3128,7 +3180,11 @@
           <t>Sanger sequencing</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
@@ -4518,7 +4574,11 @@
           <t>RT</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
@@ -5212,7 +5272,11 @@
           <t>4559 and 3097</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
@@ -6785,2484 +6849,6 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>40391923</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>227</v>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="E259" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E260" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>RT,IN</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E261" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Stanford algorithm</t>
-        </is>
-      </c>
-      <c r="E262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E263" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>40400229</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E264" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>2006-2024</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>From 1996 to 2024.</t>
-        </is>
-      </c>
-      <c r="E265" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>40431710</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Yes.</t>
-        </is>
-      </c>
-      <c r="E266" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>40431742</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E267" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>40431742</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
-        <v>1677</v>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>1667</t>
-        </is>
-      </c>
-      <c r="E268" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>40490983</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Plasma RNA.</t>
-        </is>
-      </c>
-      <c r="E269" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>40573423</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E270" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>40596906</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>ViroSeq Genotyping System</t>
-        </is>
-      </c>
-      <c r="E271" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>40596906</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Patient samples</t>
-        </is>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>40596906</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV), Abacavir (ABC), Didanosine (DDI)</t>
-        </is>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>40713598</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>HIV-1 pol</t>
-        </is>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>40763144</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>40763144</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>PR, RT, IN</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>40763144</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Sanger, NGS</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>40763144</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>AZT, ABC, 3TC, TDF, ATV, LPV, RTV, DTG</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>TDF, 3TC, DTG, ABC, ZDV, AZT, LPVr, ATVr</t>
-        </is>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>40779404</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>40779404</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>20</v>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>40779404</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>PBMC</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Whole blood</t>
-        </is>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>40779404</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>Tenofovir, Emtricitabine, Instis, NRTIs, NNRTIs</t>
-        </is>
-      </c>
-      <c r="E282" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>7 (Uncertain)</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="E283" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E284" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Not provided</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E285" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E286" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>40857111</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E287" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E288" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>2004-2021</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E289" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>RT, PR</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E290" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E291" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E292" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E293" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E294" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>40872801</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E295" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
-        </is>
-      </c>
-      <c r="E296" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>40938120</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>1048</v>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>1,260 newly diagnosed, ART-naive individuals.</t>
-        </is>
-      </c>
-      <c r="E297" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes  </t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E298" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>NC, IN</t>
-        </is>
-      </c>
-      <c r="E299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>40938996</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Sanger, NGS</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E300" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E301" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>0</v>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E302" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E303" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>Plasma samples</t>
-        </is>
-      </c>
-      <c r="E304" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>40965168</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E305" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E306" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>NGS</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>Population sequencing</t>
-        </is>
-      </c>
-      <c r="E307" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>PBMC (Whole blood OK)</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>Whole blood</t>
-        </is>
-      </c>
-      <c r="E308" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>40974886</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E309" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E310" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>NGS</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>Whole genome sequencing</t>
-        </is>
-      </c>
-      <c r="E311" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>41004608</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>Clinical specimens</t>
-        </is>
-      </c>
-      <c r="E312" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Yes (Only past sequences)</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E313" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>249 (uncertain)</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E314" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E315" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>PR, RT, IN (presumably)</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E316" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Plasma (presumably)</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E317" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E318" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E319" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E320" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>41012586</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>DTG, DRV/r</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E321" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>2022-2024</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>2023-2024</t>
-        </is>
-      </c>
-      <c r="E322" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>41023944</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>DTG (no other ARVs specified)</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E323" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E324" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>USA, Dominican Republic</t>
-        </is>
-      </c>
-      <c r="E325" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Not provided</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2019-2020</t>
-        </is>
-      </c>
-      <c r="E326" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E327" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E328" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>41056006</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E329" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E330" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C331" t="n">
-        <v>235</v>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E331" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E332" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>2018-2023</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E333" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>RT,PR,IN</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E334" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E335" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E336" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>41057785</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>AZT, D4T, TDF, ABC, DTG</t>
-        </is>
-      </c>
-      <c r="E337" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>41088231</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>Near full-length genome (NFLG), partial pol gene, vif, env</t>
-        </is>
-      </c>
-      <c r="E339" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Yes (site-directed mutants)</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>41091504</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
-      <c r="E341" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>China, United States</t>
-        </is>
-      </c>
-      <c r="E342" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>1978 to 2023</t>
-        </is>
-      </c>
-      <c r="E343" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="E344" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>NRTIs, NNRTIs</t>
-        </is>
-      </c>
-      <c r="E345" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>41093949</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
-        </is>
-      </c>
-      <c r="E346" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>PP280627- PP280757</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>PP280627 to PP280757</t>
-        </is>
-      </c>
-      <c r="E347" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>41112839</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
-        </is>
-      </c>
-      <c r="E348" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>41129268</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E349" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>64</v>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E350" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="E351" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Not provided</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>2021 to 2023</t>
-        </is>
-      </c>
-      <c r="E352" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Were samples cloned prior to sequencing?</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Yes (single genome)</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E353" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>NRTI, CAI</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>NRTIs, NNRTIs.</t>
-        </is>
-      </c>
-      <c r="E354" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>Not available (deposited 2015-2025)</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>2015-2025</t>
-        </is>
-      </c>
-      <c r="E355" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E356" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E357" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E358" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2503,14 +2503,10 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
@@ -2528,7 +2524,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2553,7 +2549,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2603,7 +2599,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2626,7 +2622,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2651,7 +2647,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2701,7 +2697,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2726,7 +2722,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2751,7 +2747,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2776,7 +2772,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2801,7 +2797,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,22 +631,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>AZT, ddI, ABC, TDF, RTV, IDV, 3TC, DLV, NFV, EFV, ATV, DRV, RAL, FTC, EVG, BIC, RPV, DOR.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -661,15 +661,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1677</v>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -679,22 +681,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40490983</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1677</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Plasma RNA.</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1029,22 +1029,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1054,22 +1054,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>2004-2021</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1079,22 +1079,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1229,12 +1229,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1254,22 +1254,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1048</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1,260 newly diagnosed, ART-naive individuals.</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1279,22 +1277,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t xml:space="preserve">Yes  </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1304,22 +1302,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN, NC, Env</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
+          <t>NC, IN</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1329,20 +1327,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1048</v>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sanger, NGS</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1,260 newly diagnosed, ART-naive individuals.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1352,22 +1352,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes  </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1377,22 +1377,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NC, IN</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1402,7 +1400,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1412,7 +1410,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1432,17 +1430,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma samples</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1457,15 +1455,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1475,22 +1475,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1500,22 +1500,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Plasma samples</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1525,22 +1525,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1550,22 +1550,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Whole genome sequencing</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1575,22 +1575,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Population sequencing</t>
+          <t>Clinical specimens</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1600,22 +1600,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PBMC (Whole blood OK)</t>
+          <t>Yes (Only past sequences)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1625,22 +1625,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>249 (uncertain)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1650,22 +1650,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Whole genome sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1675,22 +1675,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Clinical specimens</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>249 (uncertain)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>PI, INSTI, NRTI (presumably)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>DTG, DRV/r</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1825,22 +1825,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2022-2024</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1850,12 +1850,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1875,22 +1875,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1900,22 +1900,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DTG, DRV/r</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1925,22 +1925,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1950,22 +1950,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DTG (no other ARVs specified)</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2000,22 +2000,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2025,22 +2025,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Not provided</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>235</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2050,17 +2048,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2075,17 +2073,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>2018-2023</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2100,17 +2098,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2130,7 +2128,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2140,7 +2138,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2155,15 +2153,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>235</v>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2178,17 +2178,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>AZT, D4T, TDF, ABC, DTG</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2198,22 +2198,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2223,22 +2223,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Yes (site-directed mutants)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2248,22 +2248,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2273,22 +2273,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>China, United States</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2298,22 +2298,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC, DTG</t>
+          <t>1978 to 2023</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2323,22 +2323,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2348,22 +2348,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2373,22 +2373,18 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2398,22 +2394,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>PP280627- PP280757</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>PP280627 to PP280757</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2423,22 +2419,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1978 to 2023</t>
+          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2448,22 +2444,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2473,22 +2469,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> None</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>64</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2498,18 +2492,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2519,22 +2517,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PP280627- PP280757</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PP280627 to PP280757</t>
+          <t>2021 to 2023</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2544,22 +2542,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes (single genome)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2569,22 +2567,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, CAI</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, NNRTIs.</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2594,20 +2592,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>64</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Not available (deposited 2015-2025)</t>
+        </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>2015-2025</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2617,22 +2617,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2642,22 +2642,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2021 to 2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2667,150 +2667,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>41130593</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>NRTI, CAI</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NRTIs, NNRTIs.</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Not available (deposited 2015-2025)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2015-2025</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,17 +586,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2006-2024</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>From 1996 to 2024.</t>
+          <t>Yes.</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -606,12 +606,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -631,22 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1677</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AZT, ddI, ABC, TDF, RTV, IDV, 3TC, DLV, NFV, EFV, ATV, DRV, RAL, FTC, EVG, BIC, RPV, DOR.</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -656,7 +654,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -681,20 +679,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1677</v>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>ViroSeq Genotyping System</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -704,22 +704,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Patient samples</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -734,17 +734,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ViroSeq Genotyping System</t>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV), Abacavir (ABC), Didanosine (DDI)</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -754,22 +754,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40713598</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Patient samples</t>
+          <t>HIV-1 pol</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -779,22 +779,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV), Abacavir (ABC), Didanosine (DDI)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -804,7 +804,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HIV-1 pol</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -834,17 +834,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger, NGS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -854,22 +854,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -879,22 +879,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -904,22 +904,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>7 (Uncertain)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>208</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -929,7 +929,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -954,22 +954,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tenofovir, Emtricitabine, Instis, NRTIs, NNRTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -979,22 +979,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>2004-2021</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1004,22 +1004,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1154,12 +1154,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1179,22 +1179,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1048</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1,260 newly diagnosed, ART-naive individuals.</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1204,22 +1202,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t xml:space="preserve">Yes  </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1229,22 +1227,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN, NC, Env</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
+          <t>NC, IN</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1254,20 +1252,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1048</v>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sanger, NGS</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1,260 newly diagnosed, ART-naive individuals.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1277,22 +1277,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes  </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1302,22 +1302,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>RT, IN, NC, Env</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NC, IN</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1327,7 +1325,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1337,7 +1335,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1357,17 +1355,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma samples</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1382,15 +1380,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1400,22 +1400,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1425,22 +1425,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Plasma samples</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1450,22 +1450,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1475,22 +1475,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Whole genome sequencing</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1500,22 +1500,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Population sequencing</t>
+          <t>Clinical specimens</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1525,17 +1525,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (Only past sequences)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1550,22 +1550,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>249 (uncertain)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Whole genome sequencing</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1575,22 +1575,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Clinical specimens</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1630,17 +1630,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>249 (uncertain)</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>PI, INSTI, NRTI (presumably)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DTG, DRV/r</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1750,22 +1750,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DTG (no other ARVs specified)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1775,22 +1775,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1800,22 +1800,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DTG, DRV/r</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1825,7 +1825,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1855,17 +1855,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1925,22 +1925,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1950,18 +1950,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>235</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1975,17 +1973,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2005,17 +2003,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2018-2023</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2030,11 +2028,13 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>235</v>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Sanger (not stated)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>Plasma (not stated)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>AZT, D4T, TDF, ABC, DTG</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2173,22 +2173,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC, DTG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2198,7 +2198,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (site-directed mutants)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2248,22 +2248,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>China, United States</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>1978 to 2023</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1978 to 2023</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2353,17 +2353,13 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> None</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2373,18 +2369,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
+          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2394,22 +2394,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PP280627- PP280757</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PP280627 to PP280757</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2419,22 +2419,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>64</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2444,22 +2442,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2474,15 +2472,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>64</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>2021 to 2023</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2497,17 +2497,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Yes (single genome)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>NRTI, CAI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2021 to 2023</t>
+          <t>NRTIs, NNRTIs.</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2542,22 +2542,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>Not available (deposited 2015-2025)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2015-2025</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2567,22 +2567,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NRTI, CAI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Not available (deposited 2015-2025)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2622,70 +2622,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,22 +1252,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1282,17 +1282,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1307,15 +1305,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Plasma samples</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Plasma samples</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1375,22 +1375,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1430,17 +1430,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Population sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1450,22 +1450,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Whole genome sequencing</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Whole genome sequencing</t>
+          <t>Clinical specimens</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1500,22 +1500,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes (Only past sequences)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Clinical specimens</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>249 (uncertain)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>249 (uncertain)</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PI, INSTI, NRTI (presumably)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
+          <t>DTG, DRV/r</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DTG, DRV/r</t>
+          <t>DTG (no other ARVs specified)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1750,22 +1750,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DTG (no other ARVs specified)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1900,22 +1900,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1930,17 +1930,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>235</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1955,11 +1953,13 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>235</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>2018-2023</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Sanger (not stated)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sanger (not stated)</t>
+          <t>Plasma (not stated)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plasma (not stated)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>AZT, D4T, TDF, ABC, DTG</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2148,22 +2148,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC, DTG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2173,7 +2173,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (site-directed mutants)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2223,22 +2223,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>China, United States</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>1978 to 2023</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1978 to 2023</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2328,17 +2328,13 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> None</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2348,18 +2344,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
+          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2369,22 +2369,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2394,22 +2394,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>64</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2424,15 +2422,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>64</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2447,17 +2447,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Not provided</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>2021 to 2023</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Yes (single genome)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2021 to 2023</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2497,17 +2497,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>NRTI, CAI</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTIs, NNRTIs.</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2517,22 +2517,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41140464</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NRTI, CAI</t>
+          <t>Not available (deposited 2015-2025)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs.</t>
+          <t>2015-2025</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Not available (deposited 2015-2025)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2611,31 +2611,6 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>41140464</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,22 +481,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>40391923</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RT,IN</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTIs, Integrase Inhibitors (INSTIs)</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -511,17 +511,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>RT,IN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stanford algorithm</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -536,17 +536,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Stanford algorithm</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -561,17 +561,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -581,7 +581,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -606,12 +606,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes.</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -631,20 +631,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>40431710</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1677</v>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>AZT, ddI, ABC, TDF, RTV, IDV, 3TC, DLV, NFV, EFV, ATV, DRV, RAL, FTC, EVG, BIC, RPV, DOR.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -654,7 +656,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -679,22 +681,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40431742</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sanger</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1677</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ViroSeq Genotyping System</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -704,22 +704,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>40573423</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Patient samples</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -734,17 +734,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV), Abacavir (ABC), Didanosine (DDI)</t>
+          <t>ViroSeq Genotyping System</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -754,22 +754,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HIV-1 pol</t>
+          <t>Patient samples</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -779,22 +779,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>40596906</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV), Abacavir (ABC), Didanosine (DDI)</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -804,7 +804,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>40713598</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>HIV-1 pol</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -829,22 +829,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>40713598</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>ABC, 3TC, AZT (ZDV), NVP, EFV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Abacavir, Lamivudine, Tenofovir, Zidovudine, Efavirenz, Nevirapine</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -854,7 +854,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -879,22 +879,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -904,22 +904,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40763144</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>Sanger, NGS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -929,22 +929,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -954,22 +954,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -979,22 +979,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40779404</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Tenofovir, Emtricitabine, Instis, NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1004,22 +1004,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>7 (Uncertain)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>208</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1029,22 +1029,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>40857111</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2004-2021</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, PR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1154,22 +1154,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1179,20 +1179,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1048</v>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1,260 newly diagnosed, ART-naive individuals.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1202,22 +1204,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes  </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1227,22 +1229,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>40872801</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RT, IN, NC, Env</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NC, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1252,7 +1254,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1262,12 +1264,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1277,7 +1279,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938120</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1286,11 +1288,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1048</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1,260 newly diagnosed, ART-naive individuals.</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1300,22 +1302,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t xml:space="preserve">Yes  </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1325,22 +1327,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>40938996</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>RT, IN, NC, Env</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Plasma samples</t>
+          <t>NC, IN</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1355,7 +1357,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1375,22 +1377,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1400,7 +1400,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Population sequencing</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1425,22 +1425,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma samples</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1450,22 +1450,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>40965168</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Whole genome sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1475,22 +1475,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Clinical specimens</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1500,22 +1500,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1525,22 +1525,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>249 (uncertain)</t>
+          <t>PBMC (Whole blood OK)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1550,22 +1550,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>40974886</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1575,22 +1575,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Whole genome sequencing</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1600,7 +1600,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>41004608</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Clinical specimens</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1630,17 +1630,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (Only past sequences)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1655,17 +1655,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>249 (uncertain)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DTG, DRV/r</t>
+          <t>PR, RT, IN (presumably)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1725,22 +1725,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DTG (no other ARVs specified)</t>
+          <t>Plasma (presumably)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1750,12 +1750,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1775,22 +1775,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1800,22 +1800,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>PI, INSTI, NRTI (presumably)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1825,17 +1825,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41012586</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>DTG, DRV/r</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1850,22 +1850,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>41023944</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>DTG (no other ARVs specified)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1900,22 +1900,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not provided (multicenter trial)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1925,20 +1925,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>235</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1948,17 +1950,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1973,17 +1975,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1998,17 +2000,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2023,22 +2025,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>41056006</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sanger (not stated)</t>
+          <t>NRTI, INSTI, CAI</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTIs, INSTIs</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2053,17 +2055,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plasma (not stated)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2078,13 +2080,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>235</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2103,17 +2103,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>2018-2023</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC, DTG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2148,22 +2148,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT,PR,IN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2173,22 +2173,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t>Sanger (not stated)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2198,22 +2198,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Plasma (not stated)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2223,22 +2223,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2248,22 +2248,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1978 to 2023</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2273,22 +2273,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41057785</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>AZT, D4T, TDF, ABC, DTG</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2298,22 +2298,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> None</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2323,18 +2323,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>41088231</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
+          <t>Near full-length genome (NFLG), partial pol gene, vif, env</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2344,22 +2348,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes (site-directed mutants)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2369,22 +2373,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>41091504</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2394,20 +2398,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>64</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>China, United States</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2417,22 +2423,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Not applicable.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>1978 to 2023</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2442,22 +2448,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2021 to 2023</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2467,22 +2473,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2492,22 +2498,18 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>41093949</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>NRTI, CAI</t>
-        </is>
-      </c>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs.</t>
+          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2517,22 +2519,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>41112839</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Not available (deposited 2015-2025)</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2542,22 +2544,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>41129268</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2567,22 +2569,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>41130593</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>64</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2592,25 +2592,225 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2021 to 2023</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NRTI, CAI</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs.</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TDF, TAF, FTC, LEN</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Emtricitabine, Tenofovir Alafenamide, Tenofovir Disoproxil Fumarate</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>41140464</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Not available (deposited 2015-2025)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2015-2025</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,20 +458,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>18715920</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>227</v>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>ABI Prism BigDye Terminator sequencing</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -481,22 +483,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40391923</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NRTIs, Integrase Inhibitors (INSTIs)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -506,24 +508,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RT,IN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>0</v>
       </c>
@@ -531,22 +529,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stanford algorithm</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -556,22 +554,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>HQ873097-HQ873169</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -581,12 +579,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>40400229</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -606,22 +604,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -631,22 +629,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40431710</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AZT, ddI, ABC, TDF, RTV, IDV, 3TC, DLV, NFV, EFV, ATV, DRV, RAL, FTC, EVG, BIC, RPV, DOR.</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -656,12 +654,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -681,20 +679,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40431742</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1677</v>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -704,22 +704,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>40573423</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Virus isolates</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -729,22 +729,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ViroSeq Genotyping System</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -754,22 +754,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Patient samples</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -779,22 +779,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>40596906</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV), Abacavir (ABC), Didanosine (DDI)</t>
+          <t>No evidence</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -804,22 +804,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HIV-1 pol</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -829,22 +829,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>40713598</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ABC, 3TC, AZT (ZDV), NVP, EFV</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Abacavir, Lamivudine, Tenofovir, Zidovudine, Efavirenz, Nevirapine</t>
+          <t>plasma RNA</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -854,7 +854,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -879,22 +879,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -904,22 +904,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>40763144</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sanger, NGS</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>gag-pol</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -929,22 +929,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -954,22 +954,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -979,22 +979,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>40779404</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tenofovir, Emtricitabine, Instis, NRTIs, NNRTIs</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1004,22 +1004,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7 (Uncertain)</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1029,22 +1029,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40857111</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1054,22 +1054,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1079,22 +1079,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2004-2021</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1104,22 +1104,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1129,22 +1129,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>viral isolates</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1154,22 +1154,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1179,24 +1179,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>0</v>
       </c>
@@ -1204,24 +1200,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>EFV, DTG, TDF, 3TC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>0</v>
       </c>
@@ -1229,24 +1221,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>40872801</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>0</v>
       </c>
@@ -1254,24 +1242,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
-        </is>
-      </c>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>0</v>
       </c>
@@ -1279,22 +1263,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>40938120</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1048</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1,260 newly diagnosed, ART-naive individuals.</t>
-        </is>
-      </c>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2021-2022</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>0</v>
       </c>
@@ -1302,24 +1284,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes  </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>0</v>
       </c>
@@ -1327,22 +1305,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40938996</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RT, IN, NC, Env</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NC, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1352,22 +1330,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1377,20 +1355,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1400,22 +1380,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1425,22 +1405,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Plasma samples</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1450,22 +1430,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>40965168</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1475,22 +1455,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1500,22 +1480,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Population sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1525,22 +1505,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PBMC (Whole blood OK)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1550,12 +1530,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>40974886</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1565,7 +1545,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1575,22 +1555,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Whole genome sequencing</t>
+          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1600,22 +1580,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>41004608</t>
+          <t>36415058</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Clinical specimens</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1625,22 +1605,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yes (Only past sequences)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1650,22 +1630,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>249 (uncertain)</t>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Zidovudine, Lamivudine, Stavudine, Didanosine, Abacavir, Tenofovir disoproxil fumarate, Efavirenz, Nevirapine, Doravirine, Lopinavir, Ritonavir, Atazanavir, Darunavir, Saquinavir, Indinavir, Nelfinavir, Raltegravir, Elvitegravir, Dolutegravir</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1675,22 +1655,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Clinical samples</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1700,22 +1680,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PR, RT, IN (presumably)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1725,22 +1705,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>EFV, RPV, ETR, ATV/r, SQV/r, DRV/r, RAL, DTG, AZT, TDF, 3TC, FTC</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1750,12 +1730,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1765,7 +1745,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1775,22 +1755,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>120 * 76% = 95, or 120 or 129</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1800,22 +1780,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PI, INSTI, NRTI (presumably)</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1825,22 +1805,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>41012586</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DTG, DRV/r</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1850,22 +1830,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>41023944</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DTG (no other ARVs specified)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1875,7 +1855,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1900,24 +1880,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>USA, Dominican Republic</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>0</v>
       </c>
@@ -1925,24 +1901,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Not provided</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2019-2020</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
         <v>0</v>
       </c>
@@ -1950,24 +1922,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
         <v>0</v>
       </c>
@@ -1975,24 +1943,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
         <v>0</v>
       </c>
@@ -2000,22 +1964,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2025,22 +1989,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>41056006</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, CAI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2050,24 +2014,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
         <v>0</v>
       </c>
@@ -2075,22 +2035,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>235</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BIC, FTC, TAF</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
         <v>0</v>
       </c>
@@ -2098,22 +2056,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2123,17 +2081,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2148,17 +2106,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RT,PR,IN</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2173,17 +2131,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sanger (not stated)</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2198,17 +2156,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plasma (not stated)</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2223,22 +2181,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Tenofovir, lamivudine, efavirenz, nevirapine, lopinavir, ritonavir</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2248,12 +2206,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2263,7 +2221,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No, the paper does not report HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2273,22 +2231,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>41057785</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AZT, D4T, TDF, ABC, DTG</t>
+          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2298,22 +2256,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>The paper does not specify which HIV genes were sequenced.</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2323,7 +2281,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>41088231</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2333,12 +2291,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Whole genome</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Near full-length genome (NFLG), partial pol gene, vif, env</t>
+          <t>The paper does not specify the type of samples that were sequenced.</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2348,22 +2306,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
+          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The individuals received tenofovir, lamivudine/emtricitabine, and an NNRTI (efavirenz or nevirapine) before sample sequencing.</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2373,22 +2331,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>41091504</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>527</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>594</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2398,7 +2356,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2408,12 +2366,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>Data as of August 2021</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2423,22 +2381,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Not applicable.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1978 to 2023</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2448,22 +2406,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2473,22 +2431,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> None</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2498,18 +2456,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>41093949</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2519,7 +2481,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>41112839</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2529,12 +2491,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2544,22 +2506,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>41129268</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TDF, FTC, 3TC, ABC, ZDV, EVF, NVP, ATV/r, LPV/r, RAL, DTG, DRV/r, ETR, RPV, BIC, CAB</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2569,20 +2531,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>36851760</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>64</v>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>Unspecified NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2592,22 +2556,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Not provided (multicenter trial)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Viral RNA from cultured virus</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2617,22 +2581,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2021 to 2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2642,22 +2606,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Yes (single genome)</t>
+          <t>Plasma, CSF, PBMC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2667,22 +2631,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NRTI, CAI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2692,22 +2656,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>41130593</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TDF, TAF, FTC, LEN</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Emtricitabine, Tenofovir Alafenamide, Tenofovir Disoproxil Fumarate</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2717,22 +2681,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Not available (deposited 2015-2025)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2742,22 +2706,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2767,22 +2731,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>37017009</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Next-generation sequencing (Illumina MiSeq).</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2792,25 +2756,3463 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>41140464</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>37039023</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NC_001802</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>37071019</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>37104815</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>37104815</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Whole Blood, Semen</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Plasma RNA and HIV DNA</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>37112971</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>K03455 for PR-RT and INT regions</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>37147875</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>37147875</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>37147875</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir disoproxil fumarate (TDF)</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>37272233</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>37272233</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>37272233</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>37272233</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
         <is>
           <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>37272233</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>37279764</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>37279764</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Blood samples</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>37340869</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CAB, RPV</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>37358226</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>37358226</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>37376649</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Plasma; PBMC</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Whole blood</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>37381002</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs, PIs</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>37439411</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>37439411</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>EFV, NVP, RPV, ETR, DOR</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>37495103</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ABI PRISM sequencing</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>37498738</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>K03455</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>37498738</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NFLG</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Gag, Pol, Env, Integnase RT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>37498738</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, Illumina sequencing</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Next-Generation Sequencing (NGS)</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>37498738</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DTG</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>37515095</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>37515146</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>37515146</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ABI 3500</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>37515146</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DTG</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>EFV, ATV, FTC, TDF</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>37540331</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>37540331</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>37540331</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2020-2021</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>37546367</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>37593123</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>37593123</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>37626789</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>37626789</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ABI-3730 DNA genetic analyzer</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>37632026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs, P Is</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>37632026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Atazanavir (ATV/r), Darunavir (DRV/r), Efavirenz (EFV), Lopinavir (LPV/r), Nevirapine (NVP), Tenofovir (TDF), Zidovudine (AZT), Lamivudine (3TC), Emtricitabine (FTC)</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>37632071</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>37674678</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>37674678</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ABI 3730XL</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2020-2021</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NRTIs, INSTIs</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>37817087</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>4559 and 3097</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>37817087</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Serum, Plasma, DBS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Plasma, serum, dried serum, or plasma spots</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>37823653</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NFLG, Envelope</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>37823653</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>plasma viral RNA</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>37872202</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>gp120</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>None reported</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>37880705</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>37896785</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>37896785</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>d4T, 3TC, AZT, NVP</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>37896860</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>RT, PI</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, Illumina sequencing</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>MiSeq sequencing platform</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>TDF, FTC, EFV</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>37920909</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Viral RNA</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>820 or 46</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>37946329</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>37946329</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Full genome, NFLG</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>37976080</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>37976080</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>TDF, FTC</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>TDF/TAF with FTC</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>38020274</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>38020274</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>38033131</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>38033131</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>HIV from plasma</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs, Protease Inhibitors</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Plasma, PBMC</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>BIC, FTC, TAF, EVG</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>38140553</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>K03455</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>38140553</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>38140553</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs, PIs</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>38152686</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>38152686</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>High-throughput sequencing</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NRTI, PI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>38864613</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>RT, CA</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Gag, Pol</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>38864613</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Plasma viral RNA</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -513,15 +513,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
@@ -534,19 +538,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>0</v>
       </c>
@@ -634,17 +634,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -659,17 +659,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Virus isolates</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Virus isolates</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -809,17 +809,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>plasma RNA</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -834,17 +834,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PBMC, Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>plasma RNA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -884,17 +884,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -909,17 +909,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>gag-pol</t>
+          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -934,17 +934,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -959,17 +959,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
+          <t>gag-pol</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>viral isolates</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1109,17 +1109,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>viral isolates</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1226,15 +1226,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
@@ -1247,15 +1251,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
@@ -1268,12 +1276,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1289,12 +1297,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1310,19 +1318,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>2021-2022</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>0</v>
       </c>
@@ -1335,19 +1339,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>0</v>
       </c>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>EFV, RPV, ETR, ATV/r, SQV/r, DRV/r, RAL, DTG, AZT, TDF, 3TC, FTC</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1710,17 +1710,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EFV, RPV, ETR, ATV/r, SQV/r, DRV/r, RAL, DTG, AZT, TDF, 3TC, FTC</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>120 * 76% = 95, or 120 or 129</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1785,17 +1785,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>120 * 76% = 95, or 120 or 129</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1885,15 +1885,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
@@ -1906,15 +1910,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
@@ -1927,12 +1935,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1948,12 +1956,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1969,19 +1977,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
         <v>0</v>
       </c>
@@ -1994,19 +1998,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
         <v>0</v>
       </c>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>62 or 3</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
+          <t>The paper does not specify the type of samples that were sequenced.</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The paper does not specify which HIV genes were sequenced.</t>
+          <t>The individuals received tenofovir, lamivudine/emtricitabine, and an NNRTI (efavirenz or nevirapine) before sample sequencing.</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2286,17 +2286,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples that were sequenced.</t>
+          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The individuals received tenofovir, lamivudine/emtricitabine, and an NNRTI (efavirenz or nevirapine) before sample sequencing.</t>
+          <t>The paper does not specify which HIV genes were sequenced.</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Data as of August 2021</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2386,17 +2386,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>527</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>594</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Data as of August 2021</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Plasma, CSF, PBMC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plasma, CSF, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2636,17 +2636,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Whole Blood, Semen</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Plasma RNA and HIV DNA</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Whole Blood, Semen</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Plasma RNA and HIV DNA</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2907,17 +2907,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir disoproxil fumarate (TDF)</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -2957,17 +2957,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir disoproxil fumarate (TDF)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3182,17 +3182,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3207,17 +3207,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3232,17 +3232,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3257,17 +3257,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3507,17 +3507,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>Next-Generation Sequencing (NGS)</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Integnase RT</t>
+          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Next-Generation Sequencing (NGS)</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3582,17 +3582,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
+          <t>Gag, Pol, Env, Integnase RT</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3632,17 +3632,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>ABI 3500</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ABI 3500</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3682,17 +3682,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>379</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>391</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3732,17 +3732,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -3757,17 +3757,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>EFV, ATV, FTC, TDF</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3782,17 +3782,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EFV, ATV, FTC, TDF</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3857,17 +3857,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3982,17 +3982,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>PI, INSTI</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -4082,17 +4082,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PI, INSTI</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -4107,17 +4107,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -4157,17 +4157,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -4182,15 +4182,19 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
@@ -4203,17 +4207,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4228,17 +4232,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4253,17 +4257,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4278,19 +4282,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
-        </is>
-      </c>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
         <v>0</v>
       </c>
@@ -4303,17 +4303,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4328,17 +4328,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4353,17 +4353,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>ABI-3730 DNA genetic analyzer</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>551</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ABI-3730 DNA genetic analyzer</t>
+          <t>554</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4478,17 +4478,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ABI 3730XL</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4503,17 +4503,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ABI 3730XL</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4553,17 +4553,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4753,15 +4753,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>4559 and 3097</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Serum, Plasma, DBS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Plasma, serum, dried serum, or plasma spots</t>
+        </is>
+      </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
@@ -4774,19 +4778,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serum, Plasma, DBS</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Plasma, serum, dried serum, or plasma spots</t>
-        </is>
-      </c>
+          <t>4559 and 3097</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
         <v>0</v>
       </c>
@@ -4799,17 +4799,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NFLG, Envelope</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>env</t>
+          <t>plasma viral RNA</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>NFLG, Envelope</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>plasma viral RNA</t>
+          <t>env</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4874,17 +4874,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4899,17 +4899,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -5124,17 +5124,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5149,17 +5149,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5349,17 +5349,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
+          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5574,17 +5574,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>HIV from plasma</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5599,17 +5599,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>HIV from plasma</t>
+          <t>NRTIs, NNRTIs, Protease Inhibitors</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5624,17 +5624,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, Protease Inhibitors</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>BIC, FTC, TAF, EVG</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF, EVG</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5899,17 +5899,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5924,17 +5924,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -5974,17 +5974,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>High-throughput sequencing</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6049,17 +6049,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>High-throughput sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6074,17 +6074,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI</t>
+          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6174,17 +6174,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>RT, CA</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Gag, Pol</t>
+          <t>Plasma viral RNA</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6199,17 +6199,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, CA</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Plasma viral RNA</t>
+          <t>Gag, Pol</t>
         </is>
       </c>
       <c r="E234" t="n">

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:E232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -513,19 +513,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>0</v>
       </c>
@@ -538,15 +534,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
@@ -634,17 +634,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -659,17 +659,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Virus isolates</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Virus isolates</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -759,17 +759,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No evidence</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -779,22 +779,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No evidence</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -829,22 +829,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -859,17 +859,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -884,17 +884,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>gag-pol</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -934,17 +934,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -954,22 +954,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30053052</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>gag-pol</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -984,17 +984,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>K03455, AF324493</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1004,7 +1004,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>31988104</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1029,17 +1029,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>32601157</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>viral isolates</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1109,17 +1109,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>viral isolates</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1129,22 +1129,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>33855437</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1154,24 +1154,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>34516245</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Population sequencing</t>
-        </is>
-      </c>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>0</v>
       </c>
@@ -1184,12 +1180,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1200,17 +1196,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EFV, DTG, TDF, 3TC</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1226,19 +1222,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>2021-2022</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>0</v>
       </c>
@@ -1251,19 +1243,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>0</v>
       </c>
@@ -1276,15 +1264,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
@@ -1297,15 +1289,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
@@ -1313,20 +1309,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2021-2022</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
@@ -1334,20 +1334,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RT, IN</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
@@ -1360,17 +1364,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1385,17 +1389,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1410,12 +1414,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1435,12 +1439,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1460,17 +1464,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1485,17 +1489,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1510,17 +1514,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1530,22 +1534,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>36415058</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1555,22 +1559,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1580,22 +1584,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36415058</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Zidovudine, Lamivudine, Stavudine, Didanosine, Abacavir, Tenofovir disoproxil fumarate, Efavirenz, Nevirapine, Doravirine, Lopinavir, Ritonavir, Atazanavir, Darunavir, Saquinavir, Indinavir, Nelfinavir, Raltegravir, Elvitegravir, Dolutegravir</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1605,22 +1609,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Clinical samples</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1630,22 +1634,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Zidovudine, Lamivudine, Stavudine, Didanosine, Abacavir, Tenofovir disoproxil fumarate, Efavirenz, Nevirapine, Doravirine, Lopinavir, Ritonavir, Atazanavir, Darunavir, Saquinavir, Indinavir, Nelfinavir, Raltegravir, Elvitegravir, Dolutegravir</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1655,22 +1659,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>36571282</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Clinical samples</t>
+          <t>EFV, RPV, ETR, ATV/r, SQV/r, DRV/r, RAL, DTG, AZT, TDF, 3TC, FTC</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1680,22 +1684,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EFV, RPV, ETR, ATV/r, SQV/r, DRV/r, RAL, DTG, AZT, TDF, 3TC, FTC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1705,7 +1709,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1715,12 +1719,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>120 * 76% = 95, or 120 or 129</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1735,17 +1739,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1760,17 +1764,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1785,17 +1789,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>120 * 76% = 95, or 120 or 129</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1805,22 +1809,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1830,24 +1834,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RT, IN</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
         <v>0</v>
       </c>
@@ -1860,19 +1860,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
         <v>0</v>
       </c>
@@ -1885,19 +1881,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>0</v>
       </c>
@@ -1910,19 +1902,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
         <v>0</v>
       </c>
@@ -1935,15 +1923,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
@@ -1956,15 +1948,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
@@ -1977,12 +1973,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1998,12 +1994,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2014,20 +2010,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2019-2020</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
@@ -2035,20 +2035,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RT, IN</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>8 and 10</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
@@ -2061,17 +2065,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2131,22 +2135,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Tenofovir, lamivudine, efavirenz, nevirapine, lopinavir, ritonavir</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2156,22 +2160,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No, the paper does not report HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2181,22 +2185,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>36694270</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, efavirenz, nevirapine, lopinavir, ritonavir</t>
+          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2211,17 +2215,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>No, the paper does not report HIV sequences from patient samples.</t>
+          <t>The paper does not specify which HIV genes were sequenced.</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2281,7 +2285,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2291,12 +2295,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>62 or 3</t>
+          <t>527</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
+          <t>594</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2306,22 +2310,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The paper does not specify which HIV genes were sequenced.</t>
+          <t>Data as of August 2021</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2381,22 +2385,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>36738248</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2406,12 +2410,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>36738248</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2421,7 +2425,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Data as of August 2021</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2431,22 +2435,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>36779485</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2456,12 +2460,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>36795586</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2471,7 +2475,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>TDF, FTC, 3TC, ABC, ZDV, EVF, NVP, ATV/r, LPV/r, RAL, DTG, DRV/r, ETR, RPV, BIC, CAB</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2481,22 +2485,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>36851704</t>
+          <t>36851760</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unspecified NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2506,12 +2510,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>36851704</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2521,7 +2525,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TDF, FTC, 3TC, ABC, ZDV, EVF, NVP, ATV/r, LPV/r, RAL, DTG, DRV/r, ETR, RPV, BIC, CAB</t>
+          <t>Viral RNA from cultured virus</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2531,22 +2535,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>36851760</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Unspecified NRTIs, NNRTIs, PIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2556,7 +2560,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>36920025</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2566,12 +2570,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma, CSF, PBMC</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Viral RNA from cultured virus</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2586,12 +2590,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plasma, CSF, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2611,17 +2615,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2631,22 +2635,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2656,22 +2660,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2681,12 +2685,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>36961945</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2706,22 +2710,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>36967989</t>
+          <t>37017009</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Next-generation sequencing (Illumina MiSeq).</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2731,22 +2735,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>37017009</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Next-generation sequencing (Illumina MiSeq).</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2756,22 +2760,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>37029656</t>
+          <t>37039023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NC_001802</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2781,24 +2785,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>37039023</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NC_001802</t>
-        </is>
-      </c>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
         <v>0</v>
       </c>
@@ -2806,20 +2806,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>37071019</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
@@ -2852,22 +2856,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>37104815</t>
+          <t>37112971</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>K03455 for PR-RT and INT regions</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2877,22 +2881,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>37112971</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>K03455 for PR-RT and INT regions</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2952,22 +2956,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>37147875</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -2982,17 +2986,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3007,7 +3011,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3032,17 +3036,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3057,7 +3061,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3067,7 +3071,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3077,12 +3081,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3092,7 +3096,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3107,7 +3111,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3117,7 +3121,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Blood samples</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3127,22 +3131,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>37279764</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Blood samples</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3157,17 +3161,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3182,17 +3186,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3207,7 +3211,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3232,17 +3236,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3257,12 +3261,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3282,12 +3286,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3302,22 +3306,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3332,7 +3336,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3342,7 +3346,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3352,22 +3356,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>37358226</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3377,22 +3381,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>37376649</t>
+          <t>37381002</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Plasma; PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -3402,22 +3406,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>37381002</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3432,17 +3436,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>RNA</t>
+          <t>EFV, NVP, RPV, ETR, DOR</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3452,22 +3456,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>37495103</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>EFV, NVP, RPV, ETR, DOR</t>
+          <t>ABI PRISM sequencing</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3477,22 +3481,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>37495103</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ABI PRISM sequencing</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3507,17 +3511,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Next-Generation Sequencing (NGS)</t>
+          <t>Gag, Pol, Env, Integnase RT</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3532,17 +3536,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
+          <t>Next-Generation Sequencing (NGS)</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3557,17 +3561,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3577,22 +3581,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37515095</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Integnase RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3602,22 +3606,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>37515095</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>379</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>391</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3677,22 +3681,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>37515146</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3777,7 +3781,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3787,12 +3791,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3852,12 +3856,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3882,17 +3886,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3907,7 +3911,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3917,7 +3921,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3927,22 +3931,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>37540331</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -3957,17 +3961,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -3982,17 +3986,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -4007,17 +4011,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PI, INSTI</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -4032,17 +4036,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -4057,17 +4061,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>PI, INSTI</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -4082,17 +4086,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -4102,22 +4106,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37546367</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -4127,22 +4131,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4157,19 +4161,15 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
         <v>0</v>
       </c>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4207,17 +4207,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4257,17 +4257,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4277,20 +4277,24 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
@@ -4323,22 +4327,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>37593123</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>551</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>554</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4373,22 +4377,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>37626789</t>
+          <t>37632026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>NRTIs, NNRTIs, P Is</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4403,17 +4407,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, P Is</t>
+          <t>Abacavir (ABC), Atazanavir (ATV/r), Darunavir (DRV/r), Efavirenz (EFV), Lopinavir (LPV/r), Nevirapine (NVP), Tenofovir (TDF), Zidovudine (AZT), Lamivudine (3TC), Emtricitabine (FTC)</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4423,22 +4427,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>37632026</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Atazanavir (ATV/r), Darunavir (DRV/r), Efavirenz (EFV), Lopinavir (LPV/r), Nevirapine (NVP), Tenofovir (TDF), Zidovudine (AZT), Lamivudine (3TC), Emtricitabine (FTC)</t>
+          <t>NRTI, INSTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4448,22 +4452,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>37632071</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, NNRTI, PI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4498,12 +4502,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>37674678</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4528,17 +4532,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4553,17 +4557,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4578,17 +4582,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4598,22 +4602,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4623,22 +4627,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4653,17 +4657,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, INSTIs</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4678,17 +4682,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4698,24 +4702,20 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>NRTIs, INSTIs</t>
-        </is>
-      </c>
+          <t>4559 and 3097</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
         <v>0</v>
       </c>
@@ -4723,22 +4723,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Serum, Plasma, DBS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir</t>
+          <t>Plasma, serum, dried serum, or plasma spots</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4748,22 +4748,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>37817087</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serum, Plasma, DBS</t>
+          <t>NFLG, Envelope</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Plasma, serum, dried serum, or plasma spots</t>
+          <t>env</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4773,20 +4773,24 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>37817087</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>4559 and 3097</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>plasma viral RNA</t>
+        </is>
+      </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
@@ -4794,22 +4798,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37872202</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>gp120</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>plasma viral RNA</t>
+          <t>None reported</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4819,22 +4823,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NFLG, Envelope</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>env</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4844,22 +4848,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>None reported</t>
+          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -4869,22 +4873,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37880705</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4894,22 +4898,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4919,22 +4923,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>37880705</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>d4T, 3TC, AZT, NVP</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -4944,22 +4948,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37896860</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>RT, PI</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -4969,22 +4973,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>d4T, 3TC, AZT, NVP</t>
+          <t>MiSeq sequencing platform</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -4994,22 +4998,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>RT, PI</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5024,17 +5028,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>MiSeq sequencing platform</t>
+          <t>TDF, FTC, EFV</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5044,22 +5048,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Viral RNA</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5069,22 +5073,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>TDF, FTC, EFV</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5094,7 +5098,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5104,12 +5108,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
           <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Viral RNA</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5119,12 +5123,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5134,7 +5138,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5144,22 +5148,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5169,22 +5173,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -5194,22 +5198,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Full genome, NFLG</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
+          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5219,22 +5223,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5244,22 +5248,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Full genome, NFLG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
+          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5269,22 +5273,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>TDF, FTC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>TDF/TAF with FTC</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5294,22 +5298,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5319,22 +5323,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TDF, FTC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>TDF/TAF with FTC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5349,7 +5353,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5359,7 +5363,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
+          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5374,17 +5378,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5394,22 +5398,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5419,12 +5423,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5434,7 +5438,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
+          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5444,12 +5448,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5459,7 +5463,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5469,7 +5473,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5484,7 +5488,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
+          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5494,22 +5498,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5519,22 +5523,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5549,17 +5553,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>HIV from plasma</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5574,17 +5578,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>HIV from plasma</t>
+          <t>NRTIs, NNRTIs, Protease Inhibitors</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5594,22 +5598,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, Protease Inhibitors</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5619,17 +5623,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5649,17 +5653,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5674,12 +5678,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5699,12 +5703,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5724,12 +5728,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5749,12 +5753,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5774,12 +5778,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF, EVG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5799,12 +5803,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5824,12 +5828,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>BIC, FTC, TAF, EVG</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5844,22 +5848,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5869,22 +5873,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5899,17 +5903,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5919,12 +5923,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5934,7 +5938,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5944,22 +5948,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -5969,22 +5973,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -5994,22 +5998,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>High-throughput sequencing</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6024,17 +6028,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>High-throughput sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6049,17 +6053,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6074,7 +6078,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6084,7 +6088,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI</t>
+          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6094,22 +6098,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6119,22 +6123,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>RT, CA</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>Gag, Pol</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6144,75 +6148,25 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>38427738</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma viral RNA</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>38864613</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Plasma viral RNA</t>
-        </is>
-      </c>
-      <c r="E233" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>38864613</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>RT, CA</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Gag, Pol</t>
-        </is>
-      </c>
-      <c r="E234" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E232"/>
+  <dimension ref="A1:E322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18715920</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ABI Prism BigDye Terminator sequencing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -529,22 +529,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19104010</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>HQ873097-HQ873169</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -554,22 +554,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21115794</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HQ873097-HQ873169</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -584,17 +584,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -604,22 +604,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23749954</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -654,22 +654,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27009474</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Virus isolates</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -704,22 +704,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27124362</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Virus isolates</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -734,17 +734,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No evidence</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -754,22 +754,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No evidence</t>
+          <t>plasma RNA</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -804,22 +804,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PBMC, Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>plasma RNA</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -834,17 +834,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -859,17 +859,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -884,17 +884,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>gag-pol</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -909,17 +909,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>gag-pol</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -929,12 +929,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30053052</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -959,17 +959,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>K03455, AF324493</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -979,7 +979,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>31988104</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1004,22 +1004,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>32601157</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>viral isolates</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1104,22 +1104,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>33855437</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>viral isolates</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1129,24 +1129,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>34516245</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Population sequencing</t>
-        </is>
-      </c>
+          <t>NRTI, NNRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>0</v>
       </c>
@@ -1159,12 +1155,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1175,20 +1171,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EFV, DTG, TDF, 3TC</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
@@ -1201,15 +1201,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
@@ -1222,12 +1226,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1243,12 +1247,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1264,19 +1268,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>0</v>
       </c>
@@ -1284,12 +1284,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1509,22 +1509,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>36415058</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1534,22 +1534,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36415058</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1564,17 +1564,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Zidovudine, Lamivudine, Stavudine, Didanosine, Abacavir, Tenofovir disoproxil fumarate, Efavirenz, Nevirapine, Doravirine, Lopinavir, Ritonavir, Atazanavir, Darunavir, Saquinavir, Indinavir, Nelfinavir, Raltegravir, Elvitegravir, Dolutegravir</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1584,22 +1584,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Zidovudine, Lamivudine, Stavudine, Didanosine, Abacavir, Tenofovir disoproxil fumarate, Efavirenz, Nevirapine, Doravirine, Lopinavir, Ritonavir, Atazanavir, Darunavir, Saquinavir, Indinavir, Nelfinavir, Raltegravir, Elvitegravir, Dolutegravir</t>
+          <t>Clinical samples</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1609,22 +1609,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36571282</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Clinical samples</t>
+          <t>EFV, RPV, ETR, ATV/r, SQV/r, DRV/r, RAL, DTG, AZT, TDF, 3TC, FTC</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1659,22 +1659,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>36597160</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EFV, RPV, ETR, ATV/r, SQV/r, DRV/r, RAL, DTG, AZT, TDF, 3TC, FTC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1784,12 +1784,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1839,15 +1839,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
@@ -1860,12 +1864,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1881,12 +1885,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1902,12 +1906,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1923,19 +1927,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
         <v>0</v>
       </c>
@@ -1948,19 +1948,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
         <v>0</v>
       </c>
@@ -1973,12 +1969,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1989,20 +1985,24 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
@@ -2015,17 +2015,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2110,7 +2110,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Tenofovir, lamivudine, efavirenz, nevirapine, lopinavir, ritonavir</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2135,22 +2135,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36694270</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, efavirenz, nevirapine, lopinavir, ritonavir</t>
+          <t>No, the paper does not report HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No, the paper does not report HIV sequences from patient samples.</t>
+          <t>The paper does not specify the type of samples that were sequenced.</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2190,17 +2190,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>62 or 3</t>
+          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
+          <t>The individuals received tenofovir, lamivudine/emtricitabine, and an NNRTI (efavirenz or nevirapine) before sample sequencing.</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2215,17 +2215,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The paper does not specify which HIV genes were sequenced.</t>
+          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples that were sequenced.</t>
+          <t>The paper does not specify which HIV genes were sequenced.</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2260,22 +2260,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TDF, 3TC, FTC, EFV, NVP, DTG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The individuals received tenofovir, lamivudine/emtricitabine, and an NNRTI (efavirenz or nevirapine) before sample sequencing.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>527</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Data as of August 2021</t>
+          <t>594</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Data as of August 2021</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2360,22 +2360,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>36738248</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2385,22 +2385,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>36779485</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2410,22 +2410,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>36795586</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TDF, FTC, 3TC, ABC, ZDV, EVF, NVP, ATV/r, LPV/r, RAL, DTG, DRV/r, ETR, RPV, BIC, CAB</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2460,7 +2460,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>36851704</t>
+          <t>36851760</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TDF, FTC, 3TC, ABC, ZDV, EVF, NVP, ATV/r, LPV/r, RAL, DTG, DRV/r, ETR, RPV, BIC, CAB</t>
+          <t>Unspecified NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2485,12 +2485,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>36851760</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Unspecified NRTIs, NNRTIs, PIs</t>
+          <t>Viral RNA from cultured virus</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2510,7 +2510,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>36920025</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma, CSF, PBMC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Viral RNA from cultured virus</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2565,17 +2565,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Plasma, CSF, PBMC</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2610,22 +2610,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2660,12 +2660,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36961945</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2685,22 +2685,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>36967989</t>
+          <t>37017009</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Next-generation sequencing (Illumina MiSeq).</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2710,22 +2710,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>37017009</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Next-generation sequencing (Illumina MiSeq).</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2735,22 +2735,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>37029656</t>
+          <t>37039023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NC_001802</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2760,24 +2760,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>37039023</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NC_001802</t>
-        </is>
-      </c>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
         <v>0</v>
       </c>
@@ -2785,20 +2781,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>37071019</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Whole Blood, Semen</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Plasma RNA and HIV DNA</t>
+        </is>
+      </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
@@ -2831,22 +2831,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>37104815</t>
+          <t>37112971</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Whole Blood, Semen</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Plasma RNA and HIV DNA</t>
+          <t>K03455 for PR-RT and INT regions</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2856,12 +2856,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>37112971</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>K03455 for PR-RT and INT regions</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir disoproxil fumarate (TDF)</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2931,22 +2931,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>37147875</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir disoproxil fumarate (TDF)</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3056,12 +3056,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Blood samples</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3106,22 +3106,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37279764</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Blood samples</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3236,17 +3236,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3281,22 +3281,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3331,22 +3331,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>37358226</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3356,22 +3356,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>37376649</t>
+          <t>37381002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3381,22 +3381,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>37381002</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>RNA</t>
+          <t>EFV, NVP, RPV, ETR, DOR</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3431,22 +3431,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>37495103</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EFV, NVP, RPV, ETR, DOR</t>
+          <t>ABI PRISM sequencing</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3456,7 +3456,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>37495103</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ABI PRISM sequencing</t>
+          <t>Next-Generation Sequencing (NGS)</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3486,17 +3486,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Integnase RT</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Next-Generation Sequencing (NGS)</t>
+          <t>Gag, Pol, Env, Integnase RT</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3556,22 +3556,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37515095</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3581,22 +3581,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>37515095</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>ABI 3500</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>379</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ABI 3500</t>
+          <t>391</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3656,22 +3656,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>37515146</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3686,17 +3686,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>EFV, ATV, FTC, TDF</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -3736,17 +3736,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -3756,22 +3756,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37537871</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>EFV, ATV, FTC, TDF</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3831,7 +3831,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>37537871</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3906,22 +3906,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>37540331</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3961,17 +3961,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>PI, INSTI</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PI, INSTI</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -4081,7 +4081,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37546367</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
+          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -4106,22 +4106,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4161,15 +4161,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
@@ -4182,17 +4186,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4207,17 +4211,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4232,19 +4236,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>NRTI, NNRTI, PI</t>
-        </is>
-      </c>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
         <v>0</v>
       </c>
@@ -4252,22 +4252,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4302,22 +4302,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>37593123</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>ABI-3730 DNA genetic analyzer</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4352,22 +4352,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>37626789</t>
+          <t>37632026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ABI-3730 DNA genetic analyzer</t>
+          <t>NRTIs, NNRTIs, P Is</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, P Is</t>
+          <t>Abacavir (ABC), Atazanavir (ATV/r), Darunavir (DRV/r), Efavirenz (EFV), Lopinavir (LPV/r), Nevirapine (NVP), Tenofovir (TDF), Zidovudine (AZT), Lamivudine (3TC), Emtricitabine (FTC)</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4402,22 +4402,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>37632026</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Atazanavir (ATV/r), Darunavir (DRV/r), Efavirenz (EFV), Lopinavir (LPV/r), Nevirapine (NVP), Tenofovir (TDF), Zidovudine (AZT), Lamivudine (3TC), Emtricitabine (FTC)</t>
+          <t>NRTI, INSTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4427,22 +4427,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>37632071</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, NNRTI, PI</t>
+          <t>ABI 3730XL</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4477,22 +4477,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>37674678</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ABI 3730XL</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4507,17 +4507,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4577,7 +4577,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, INSTIs</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs</t>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4677,22 +4677,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Serum, Plasma, DBS</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir</t>
+          <t>Plasma, serum, dried serum, or plasma spots</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4723,7 +4723,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>37817087</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serum, Plasma, DBS</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Plasma, serum, dried serum, or plasma spots</t>
+          <t>plasma viral RNA</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4773,22 +4773,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37872202</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>gp120</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>plasma viral RNA</t>
+          <t>None reported</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4798,22 +4798,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>None reported</t>
+          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4848,22 +4848,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37880705</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -4873,22 +4873,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>37880705</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>d4T, 3TC, AZT, NVP</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4923,22 +4923,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37896860</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>d4T, 3TC, AZT, NVP</t>
+          <t>RT, PI</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -4948,22 +4948,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>RT, PI</t>
+          <t>MiSeq sequencing platform</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>MiSeq sequencing platform</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>TDF, FTC, EFV</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5023,22 +5023,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>TDF, FTC, EFV</t>
+          <t>Viral RNA</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5048,7 +5048,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
           <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Viral RNA</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5098,12 +5098,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5148,22 +5148,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Full genome, NFLG</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -5198,22 +5198,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Full genome, NFLG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5248,7 +5248,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>TDF, FTC</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
+          <t>TDF/TAF with FTC</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5273,22 +5273,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TDF, FTC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>TDF/TAF with FTC</t>
+          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5373,12 +5373,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5423,12 +5423,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5473,22 +5473,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5503,17 +5503,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>HIV from plasma</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5548,22 +5548,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>HIV from plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5573,22 +5573,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, Protease Inhibitors</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>BIC, FTC, TAF, EVG</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5798,22 +5798,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5823,22 +5823,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF, EVG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5873,22 +5873,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5898,12 +5898,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5923,22 +5923,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>High-throughput sequencing</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5948,22 +5948,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -5978,17 +5978,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>High-throughput sequencing</t>
+          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6028,17 +6028,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6048,22 +6048,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6073,12 +6073,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
+          <t>Plasma viral RNA</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6098,22 +6098,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>38427738</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>RT, CA</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Gag, Pol</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6123,22 +6123,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>38864613</t>
+          <t>40391923</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>RT, CA</t>
+          <t>227</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Gag, Pol</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6148,25 +6148,2267 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>38864613</t>
+          <t>40400229</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Stanford algorithm</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
           <t>What type of samples were sequenced?</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Plasma viral RNA</t>
-        </is>
-      </c>
-      <c r="E232" t="n">
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>40400229</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>RT,IN</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>40431710</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>AZT, ddI, ABC, TDF, RTV, IDV, 3TC, DLV, NFV, EFV, ATV, DRV, RAL, FTC, EVG, BIC, RPV, DOR.</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>40431742</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>1667</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>40573423</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Patient samples</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>40596906</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV), Abacavir (ABC), Didanosine (DDI)</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>40713598</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>HIV-1 pol</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Sanger, NGS</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>AZT, ABC, 3TC, TDF, ATV, LPV, RTV, DTG</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, DTG, ABC, ZDV, AZT, LPVr, ATVr</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>40763144</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Whole blood</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>40779404</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Tenofovir, Emtricitabine, Instis, NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>40857111</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>7 (Uncertain)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2004-2021</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>40872801</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>A total of 1,048 eligible pol sequences were analyzed.</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>40938120</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>1,260 newly diagnosed, ART-naive individuals.</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes  </t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>40938996</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>RT, IN, NC, Env</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NC, IN</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Plasma samples</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>40965168</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Population sequencing</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>PBMC (Whole blood OK)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Whole blood</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>40974886</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Whole genome sequencing</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Clinical specimens</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>41004608</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Whole genome sequences</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Yes (Only past sequences)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Plasma (presumably)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>PI, INSTI, NRTI (presumably)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>DTG, DRV/r</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>249 (uncertain)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>41012586</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>PR, RT, IN (presumably)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>41023944</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>DTG (no other ARVs specified)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>USA, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>41056006</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Sanger (not stated)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Plasma (not stated)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>AZT, D4T, TDF, ABC, DTG</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2018-2023</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>41057785</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>41088231</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Near full-length genome (NFLG), partial pol gene, vif, env</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Yes (site-directed mutants)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>41091504</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> None</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NRTI: azvudine, zidovudine, lamivudine, tenofovir DF, abacavir, emtricitabine; NNRTI: nevirapine, etravirine, efavirenz</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>China, United States</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>41093949</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1978 to 2023</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>41112839</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Big Dye Terminator v3.1 and ABI 3100 Avant sequencer</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>41129268</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>NRTI, CAI</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs.</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Not provided (multicenter trial)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2021 to 2023</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>41130593</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>41140464</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Not available (deposited 2015-2025)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2015-2025</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
         <v>0</v>
       </c>
     </row>
